--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1e034028d09796c/Desktop/IKS_Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_F25DC773A252ABDACC1048E4519A6F165BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09090153-ED84-40CF-A2B5-E0CFC413E8C6}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC1048E4519A6F165BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{870EF7C6-77DB-49C0-9BD3-8F1564618072}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="488">
   <si>
     <t>Voucher No</t>
   </si>
@@ -896,6 +896,1129 @@
   </si>
   <si>
     <t>It is used to treat diarrhea, skin infections, insomnia, anxiety, and digestive issues</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/1</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/2</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/3</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/4</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/5</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/6</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/7</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/8</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/9</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/10</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/11</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/12</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/13</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/14</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/15</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/16</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/17</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/18</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/19</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/20</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/21</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/22</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/23</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/24</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/25</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/26</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/27</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/28</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/29</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/30</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/31</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/32</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/33</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/34</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/35</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/36</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/37</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/38</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/39</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/40</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/41</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/42</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/43</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/44</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/45</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/46</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/47</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/48</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/49</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/50</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/51</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/52</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/53</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/54</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/55</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/56</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/57</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/58</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/59</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/60</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/61</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/62</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/63</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/64</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/65</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/66</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/67</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/68</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/69</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/70</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/71</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/72</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/73</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/74</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/75</t>
+  </si>
+  <si>
+    <t>Acalypha indica</t>
+  </si>
+  <si>
+    <t>Aerva lanata</t>
+  </si>
+  <si>
+    <t>Ageratum conyzoides</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Allium sativum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Alocasia macrorrhizos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (L.) G. Don</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Alstonia scholaris</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (L.) R. Br</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Alternanthera sessilis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (L.) R. Br. ex DC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Amaranthus spinosus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Asparagus racemosus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Willd</t>
+    </r>
+  </si>
+  <si>
+    <t>Bauhinia vahlii</t>
+  </si>
+  <si>
+    <t>Begonia picta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bidens biternata </t>
+  </si>
+  <si>
+    <t>Borassus flabellifer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Carica papaya</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L.</t>
+    </r>
+  </si>
+  <si>
+    <t>Chromolaena odorata</t>
+  </si>
+  <si>
+    <t>Cleome rutidosperma</t>
+  </si>
+  <si>
+    <t>Clitoria ternatea</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Curculigo orchioides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Gaertn</t>
+    </r>
+  </si>
+  <si>
+    <t>Cyanthillium cinereum</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cyperus rotundus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Desmodium triflorum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> DC</t>
+    </r>
+  </si>
+  <si>
+    <t>Emilia sonchifolia</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Euphorbia hirta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Euphorbia tirucalli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ficus hispida </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>L. f.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ficus semicordata </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Foeniculum vulgare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Mill.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Hemidesmus indicus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (L.) R. Br</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Homonoia riparia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Lour. </t>
+    </r>
+  </si>
+  <si>
+    <t>Indigofera cassioides</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ipomoea digitata </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Auct.non L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Jatropha curcas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Lagenaria siceraria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Molina) Standley</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Launaea splenifolia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> DC</t>
+    </r>
+  </si>
+  <si>
+    <t>Lepidium sativum</t>
+  </si>
+  <si>
+    <t>Mangifera indica</t>
+  </si>
+  <si>
+    <t>Mimosa pudica</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Momordica charantia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+  </si>
+  <si>
+    <t>Momordica dioica</t>
+  </si>
+  <si>
+    <t>Nigella sativa</t>
+  </si>
+  <si>
+    <t>Nyctanthes arbor-tristis</t>
+  </si>
+  <si>
+    <t>Ocimum sanctum</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Opuntia elatior </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mill.</t>
+    </r>
+  </si>
+  <si>
+    <t>Phyllanthus emblica</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Pueraria tuberosa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> DC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ricinus communis </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>L.</t>
+    </r>
+  </si>
+  <si>
+    <t>Scoparia dulcis</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Sesamum orientale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L.</t>
+    </r>
+  </si>
+  <si>
+    <t>Shorea robusta</t>
+  </si>
+  <si>
+    <t>Sida acuta</t>
+  </si>
+  <si>
+    <t>Sida cordifolia</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Smithia conferta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> JE.Smith</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Vitex negundo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> L</t>
+    </r>
+  </si>
+  <si>
+    <t>Wedelia trilobata</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Withania somnifera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (L.)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ziziphus jujuba</t>
+  </si>
+  <si>
+    <t>Ziziphus oenoplia</t>
+  </si>
+  <si>
+    <t>Euphorbiaceae</t>
+  </si>
+  <si>
+    <t>Amaranthaceae</t>
+  </si>
+  <si>
+    <t>Liliaceae</t>
+  </si>
+  <si>
+    <t>Araceae</t>
+  </si>
+  <si>
+    <t>Apocynaceae</t>
+  </si>
+  <si>
+    <t>Begoniaceae</t>
+  </si>
+  <si>
+    <t>Arecaceae</t>
+  </si>
+  <si>
+    <t>Caricaceae</t>
+  </si>
+  <si>
+    <t>Amaryllidaceae</t>
+  </si>
+  <si>
+    <t>Cyperaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apiaceae </t>
+  </si>
+  <si>
+    <t>Convolvulaceae</t>
+  </si>
+  <si>
+    <t>Cucurbitaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asteraceae </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brassicaceae </t>
+  </si>
+  <si>
+    <t>Ranunculaceae</t>
+  </si>
+  <si>
+    <t>Oleaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phyllanthaceae </t>
+  </si>
+  <si>
+    <t>Plantaginaceae</t>
+  </si>
+  <si>
+    <t>Pedaleaceae</t>
+  </si>
+  <si>
+    <t>Dipterocarpaceae</t>
+  </si>
+  <si>
+    <t>Astraceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solanaceae </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhamnaceae </t>
+  </si>
+  <si>
+    <t>It is used to treat skin diseases, respiratory issues and gastrointestinal conditions</t>
+  </si>
+  <si>
+    <t>It acts as a demulcent, anthelmintic, anti-inflammatory, and antidiabetic agent</t>
+  </si>
+  <si>
+    <t>It is used to treat wounds, infections, and inflammatory conditions</t>
+  </si>
+  <si>
+    <t>It is used for treating skin diseases, leprosy, asthma, and inflammatory conditions</t>
+  </si>
+  <si>
+    <t>It is used as antimicrobial, anticancer, antioxidant and anti-diabetic agent</t>
+  </si>
+  <si>
+    <t>It is used to cure rheumatism, snake bites and toothache</t>
+  </si>
+  <si>
+    <t>It has antidiabetic, antibacterial, antianxiety and anticancer properties</t>
+  </si>
+  <si>
+    <t>Wound healing activity and treatment against  gonorrhoea</t>
+  </si>
+  <si>
+    <t>It is used as antipyretic, laxative, diuretic, digestible, anti-diabetic, anti-snake venom</t>
+  </si>
+  <si>
+    <t>It is used for treatment of gastric ulcers, neurological disorders and lactation as galactogogue</t>
+  </si>
+  <si>
+    <t>It has anti-diabetic, anti-inflammatory, antioxidant, and antibacterial properties</t>
+  </si>
+  <si>
+    <t>It is used for treatment of diaroohea, stomach disease headache, Respiratory disorders</t>
+  </si>
+  <si>
+    <t>It is used to treat inflammation, respiratory issues, digestive disorders, liver ailments</t>
+  </si>
+  <si>
+    <t>It is used to treat inflammatory, digestive, and respiratory disorders, alongside providing antimicrobial and antioxidant benefits</t>
+  </si>
+  <si>
+    <t>Used for treatment of fever, pyrexia, diabetes, gonorrhea, syphilis, inflammation</t>
+  </si>
+  <si>
+    <t>It has anti microbial and wound healing properties</t>
+  </si>
+  <si>
+    <t>It is used to treat ear infections, convulsions, and skin inflammation</t>
+  </si>
+  <si>
+    <t>It has antioxidant, and anti-inflammatory properties</t>
+  </si>
+  <si>
+    <t>It is used as immunostimulant, hepatoprotective, anti-oxidant</t>
+  </si>
+  <si>
+    <t>It acts as an anti-inflammatory, antioxidant, and analgesic agent</t>
+  </si>
+  <si>
+    <t>Locally used to treat  diarrhea, diabetes</t>
+  </si>
+  <si>
+    <t>To treat diarrhea, dysentery, convulsions, cough, bronchitis, and skin infections</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antioxidant, antimicrobial, and analgesic properties</t>
+  </si>
+  <si>
+    <t>It is traditionally for female disorders, respiratory ailments (cough, coryza, bronchitis, and asthma), worm infestations</t>
+  </si>
+  <si>
+    <t>It is useful in whooping cough, gonorrhea, asthma, leprosy, dropsy, dyspepsia, enlargement of spleen</t>
+  </si>
+  <si>
+    <t>It is used in culinary and has anti-allergic, analgesic, anti- inflammatory, antioxidant, antibacterial properties</t>
+  </si>
+  <si>
+    <t>Used to purify blood, treat skin diseases, infections, and liver disorders</t>
+  </si>
+  <si>
+    <t>Used in traditional medicine for its diuretic, laxative, and anti-inflammatory attributes</t>
+  </si>
+  <si>
+    <t>It is used as hypoglycemic, anti-inflammatory, anticonvulsant, and aphrodisiac agent</t>
+  </si>
+  <si>
+    <t>It is used to treat skin, cancer, digestive, respiratory and infectious diseases. It is also used to produce biofuel, soap</t>
+  </si>
+  <si>
+    <t>It has cardioprotective, antidote, aphrodisiac, cardiotonic, diuretic, and general tonic properties</t>
+  </si>
+  <si>
+    <t>It has anti-oxidant, hepatoprotective, anti-cancer, anti-nociceptive, anti-inflammatory properties</t>
+  </si>
+  <si>
+    <t>Used in folk medicine for treatment of asthma, bronchitis and cough</t>
+  </si>
+  <si>
+    <t>It is used as a dentrifrice, antiseptic, astringent, diaphoretic, stomachic, vermifuge, tonic, laxative</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antimicrobial, and wound-healing attributes</t>
+  </si>
+  <si>
+    <t>It has antioxidant, antiparasitic, anti-inflammatory, antibacterial, antidiabetic properties</t>
+  </si>
+  <si>
+    <t>It has anti-diabetic, anti-inflammatory, antioxidant, and hepatoprotective properties</t>
+  </si>
+  <si>
+    <t>Support immune, respiratory, and digestive health</t>
+  </si>
+  <si>
+    <t>It is used for joint pain,  fevers, respiratory issues, digestive ailments</t>
+  </si>
+  <si>
+    <t>It is used to treat respiratory ailments, reduce anxiety, and manage fever</t>
+  </si>
+  <si>
+    <t>Used for treatment of diabetes, obesity, asthma, inflammatory disorders</t>
+  </si>
+  <si>
+    <t>It has analgesic, anti-inflammatory, antimicrobial, anti-diarrheal and cytotoxic effects</t>
+  </si>
+  <si>
+    <t>It has anticancer, anticonvulsant, antidiabetic, antifertility, anti-inflammatory</t>
+  </si>
+  <si>
+    <t>Used in inflammation treatment, liver disorders, hypoglycemic, and as a laxative</t>
+  </si>
+  <si>
+    <t>It is used to treat diabetes, hypertension, bronchitis, gastric ulcers, and skin infections</t>
+  </si>
+  <si>
+    <t>It is used as oil and as digestive, antispasmodic,  tonic, diuretic, and gastrointestinal disorders</t>
+  </si>
+  <si>
+    <t>It is used in treating non healing wounds, diabetes, boils, deafness</t>
+  </si>
+  <si>
+    <t>It is used to treat infections, abscesses, headaches, fever, digestive issues and pain</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, analgesic, and nervine tonic properties</t>
+  </si>
+  <si>
+    <t>It is used as laxative, enhancing fertility, treatment of rheumatism</t>
+  </si>
+  <si>
+    <t>It is used in cephalgia, otalgia, arthritis, inflammation, rheumatism, skin diseases</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antibacterial, wound-healing, and antioxidant properties</t>
+  </si>
+  <si>
+    <t>It is used for treatment of hypertension, stress, diabetes, asthma</t>
+  </si>
+  <si>
+    <t>It supports liver health and used to treat insomnia, anxiety, and depression</t>
+  </si>
+  <si>
+    <t>Treatment of digestive disorders, urinary troubles, diabetes</t>
   </si>
 </sst>
 </file>
@@ -983,7 +2106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1020,6 +2143,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1301,7 +2442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -2417,6 +3558,1056 @@
         <v>276</v>
       </c>
     </row>
+    <row r="80" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="D84" s="17" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="D85" s="17" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="D86" s="17" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="D87" s="17" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="D88" s="17" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="D93" s="17" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="D95" s="17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D96" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D97" s="17" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D101" s="17" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D103" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D104" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="D105" s="17" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D106" s="17" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="D107" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="17" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D109" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D110" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D111" s="17" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="D112" s="17" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="D113" s="17" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D114" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D115" s="17" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="D116" s="17" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" s="17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="D118" s="17" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="D119" s="17" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="D121" s="17" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="D122" s="17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="D123" s="17" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="D124" s="17" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B125" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="D125" s="17" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B126" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B127" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D127" s="17" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B128" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C128" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="D129" s="17" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D132" s="17" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B133" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="C133" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D133" s="17" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B135" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="C135" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="D135" s="17" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B137" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="D137" s="17" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C138" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D138" s="17" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B139" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C139" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="D139" s="17" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="C140" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="D140" s="17" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C141" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="D141" s="17" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="D142" s="17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B143" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="C143" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D143" s="17" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="C144" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D144" s="17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C145" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D145" s="17" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B146" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D146" s="17" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B147" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D147" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D148" s="17" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B149" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D149" s="17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C150" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B151" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="C151" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="D151" s="17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="D152" s="17" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B153" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C153" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="D153" s="17" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="C154" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="D154" s="17" t="s">
+        <v>487</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1e034028d09796c/Desktop/IKS_Document/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website-Project\IKS\iks-digital-repository\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC1048E4519A6F165BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{870EF7C6-77DB-49C0-9BD3-8F1564618072}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBFA22D-75F5-4BC5-BE2B-1F6A5EB0E28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="606">
   <si>
     <t>Voucher No</t>
   </si>
@@ -2019,6 +2019,360 @@
   </si>
   <si>
     <t>Treatment of digestive disorders, urinary troubles, diabetes</t>
+  </si>
+  <si>
+    <t>Local Name</t>
+  </si>
+  <si>
+    <t>Ankula</t>
+  </si>
+  <si>
+    <t>Dhalasiris</t>
+  </si>
+  <si>
+    <t>Gopal saga</t>
+  </si>
+  <si>
+    <t>Chirkuti</t>
+  </si>
+  <si>
+    <t>Khada saga</t>
+  </si>
+  <si>
+    <t>Dhaura</t>
+  </si>
+  <si>
+    <t>Mathasaga</t>
+  </si>
+  <si>
+    <t>Neem</t>
+  </si>
+  <si>
+    <t>Helta</t>
+  </si>
+  <si>
+    <t>Kolieri</t>
+  </si>
+  <si>
+    <t>Simili</t>
+  </si>
+  <si>
+    <t>Chara</t>
+  </si>
+  <si>
+    <t>Palash</t>
+  </si>
+  <si>
+    <t>Chatani Kalra</t>
+  </si>
+  <si>
+    <t>Kumbhi</t>
+  </si>
+  <si>
+    <t>Sunari</t>
+  </si>
+  <si>
+    <t>Chakunda</t>
+  </si>
+  <si>
+    <t>Sirgitisaga</t>
+  </si>
+  <si>
+    <t>Karada</t>
+  </si>
+  <si>
+    <t>Chermaiyaa</t>
+  </si>
+  <si>
+    <t>Saruani aa</t>
+  </si>
+  <si>
+    <t>Kanna aa</t>
+  </si>
+  <si>
+    <t>Nagachampa</t>
+  </si>
+  <si>
+    <t>Dudhi lata</t>
+  </si>
+  <si>
+    <t>Dimbu</t>
+  </si>
+  <si>
+    <t>Jeera</t>
+  </si>
+  <si>
+    <t>Haladi</t>
+  </si>
+  <si>
+    <t>Sissoo</t>
+  </si>
+  <si>
+    <t>Oou</t>
+  </si>
+  <si>
+    <t>Rai</t>
+  </si>
+  <si>
+    <t>Pita alu</t>
+  </si>
+  <si>
+    <t>Mankadakendu</t>
+  </si>
+  <si>
+    <t>Kendu</t>
+  </si>
+  <si>
+    <t>Ledung Aa(Fern)</t>
+  </si>
+  <si>
+    <t>Pannir</t>
+  </si>
+  <si>
+    <t>Paraspipal</t>
+  </si>
+  <si>
+    <t>Bara</t>
+  </si>
+  <si>
+    <t>Kagsha</t>
+  </si>
+  <si>
+    <t>Osta</t>
+  </si>
+  <si>
+    <t>Bhuindimri</t>
+  </si>
+  <si>
+    <t>Burei, Burudi</t>
+  </si>
+  <si>
+    <t>Kurum</t>
+  </si>
+  <si>
+    <t>Churla</t>
+  </si>
+  <si>
+    <t>Champati</t>
+  </si>
+  <si>
+    <t>Girli</t>
+  </si>
+  <si>
+    <t>Topia</t>
+  </si>
+  <si>
+    <t>Mahul</t>
+  </si>
+  <si>
+    <t>Mahula</t>
+  </si>
+  <si>
+    <t>Karanja</t>
+  </si>
+  <si>
+    <t>Baula</t>
+  </si>
+  <si>
+    <t>Gudikaima</t>
+  </si>
+  <si>
+    <t>Achu</t>
+  </si>
+  <si>
+    <t>Bhadunia</t>
+  </si>
+  <si>
+    <t>Chundul</t>
+  </si>
+  <si>
+    <t>Fanfana</t>
+  </si>
+  <si>
+    <t>Kathakusum</t>
+  </si>
+  <si>
+    <t>Piasal</t>
+  </si>
+  <si>
+    <t>Sankam</t>
+  </si>
+  <si>
+    <t>Ashoka</t>
+  </si>
+  <si>
+    <t>Kusum</t>
+  </si>
+  <si>
+    <t>Bhalia</t>
+  </si>
+  <si>
+    <t>Pinj</t>
+  </si>
+  <si>
+    <t>Genduli</t>
+  </si>
+  <si>
+    <t>Pamphunia</t>
+  </si>
+  <si>
+    <t>Phutkoli</t>
+  </si>
+  <si>
+    <t>Jamu</t>
+  </si>
+  <si>
+    <t>Jojo</t>
+  </si>
+  <si>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Bahada</t>
+  </si>
+  <si>
+    <t>Harida</t>
+  </si>
+  <si>
+    <t>Asan</t>
+  </si>
+  <si>
+    <t>Phasi</t>
+  </si>
+  <si>
+    <t>Kechha aa</t>
+  </si>
+  <si>
+    <t>Bishalya Karani</t>
+  </si>
+  <si>
+    <t>Kuruma</t>
+  </si>
+  <si>
+    <t>Barakoli</t>
+  </si>
+  <si>
+    <t>Habitat</t>
+  </si>
+  <si>
+    <t>Shrub</t>
+  </si>
+  <si>
+    <t>Tree</t>
+  </si>
+  <si>
+    <t>Herb</t>
+  </si>
+  <si>
+    <t>Woody grass</t>
+  </si>
+  <si>
+    <t>Succulent</t>
+  </si>
+  <si>
+    <t>Collection Area</t>
+  </si>
+  <si>
+    <t>Tamalabandh (Mayurbhanj)</t>
+  </si>
+  <si>
+    <t>Edelbeda (Mayurbhanj)</t>
+  </si>
+  <si>
+    <t>Bisipur (Mayurbhanj)</t>
+  </si>
+  <si>
+    <t>Dhalabani (Mayurbhanj)</t>
+  </si>
+  <si>
+    <t>Jarasahi (Mayurbhanj)</t>
+  </si>
+  <si>
+    <t>Mankadbeda (Mayurbhanj)</t>
+  </si>
+  <si>
+    <t>Kaliajiani (Mayurbhanj)</t>
+  </si>
+  <si>
+    <t>Plant Parts Used</t>
+  </si>
+  <si>
+    <t>Leaves &amp; fruit</t>
+  </si>
+  <si>
+    <t>Bark</t>
+  </si>
+  <si>
+    <t>Leaf, Root</t>
+  </si>
+  <si>
+    <t>Leaf</t>
+  </si>
+  <si>
+    <t>Leaves, bark</t>
+  </si>
+  <si>
+    <t>Germinated plant/shoot</t>
+  </si>
+  <si>
+    <t>Young shoot</t>
+  </si>
+  <si>
+    <t>Flower</t>
+  </si>
+  <si>
+    <t>Leaves</t>
+  </si>
+  <si>
+    <t>Whole plant</t>
+  </si>
+  <si>
+    <t>Fruits</t>
+  </si>
+  <si>
+    <t>Leaves, roots and fruits</t>
+  </si>
+  <si>
+    <t>Root, srem bark and Leaf</t>
+  </si>
+  <si>
+    <t>Fruit, Leaf</t>
+  </si>
+  <si>
+    <t>Dry fruit</t>
+  </si>
+  <si>
+    <t>Rhizome</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Tuber</t>
+  </si>
+  <si>
+    <t>Latex</t>
+  </si>
+  <si>
+    <t>Leaves &amp; bark</t>
+  </si>
+  <si>
+    <t>Fruit,Flower,seed</t>
+  </si>
+  <si>
+    <t>Seed</t>
+  </si>
+  <si>
+    <t>Leaf, fruit &amp; bark</t>
+  </si>
+  <si>
+    <t>Fruit, Seed</t>
+  </si>
+  <si>
+    <t>Gum</t>
+  </si>
+  <si>
+    <t>Leaf, seed, fruit</t>
   </si>
 </sst>
 </file>
@@ -2065,7 +2419,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2075,6 +2429,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2106,7 +2466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2131,9 +2491,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2161,6 +2518,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2442,16 +2817,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="56.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2464,8 +2843,20 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E1" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>565</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2478,8 +2869,20 @@
       <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E2" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -2492,8 +2895,20 @@
       <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E3" s="20" t="s">
+        <v>490</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -2506,8 +2921,20 @@
       <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E4" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -2520,8 +2947,20 @@
       <c r="D5" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E5" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -2534,8 +2973,20 @@
       <c r="D6" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E6" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -2548,8 +2999,20 @@
       <c r="D7" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E7" s="20" t="s">
+        <v>494</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -2562,8 +3025,20 @@
       <c r="D8" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E8" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -2576,8 +3051,20 @@
       <c r="D9" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E9" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>34</v>
       </c>
@@ -2590,8 +3077,20 @@
       <c r="D10" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E10" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>569</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>38</v>
       </c>
@@ -2604,8 +3103,20 @@
       <c r="D11" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E11" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>569</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -2618,8 +3129,20 @@
       <c r="D12" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E12" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>44</v>
       </c>
@@ -2632,8 +3155,20 @@
       <c r="D13" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E13" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>48</v>
       </c>
@@ -2646,8 +3181,20 @@
       <c r="D14" s="5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E14" s="20" t="s">
+        <v>500</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>52</v>
       </c>
@@ -2660,8 +3207,20 @@
       <c r="D15" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E15" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>55</v>
       </c>
@@ -2674,8 +3233,20 @@
       <c r="D16" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E16" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>570</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>59</v>
       </c>
@@ -2688,8 +3259,20 @@
       <c r="D17" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E17" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>63</v>
       </c>
@@ -2702,8 +3285,20 @@
       <c r="D18" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E18" s="20" t="s">
+        <v>504</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>66</v>
       </c>
@@ -2716,8 +3311,20 @@
       <c r="D19" s="8" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E19" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>69</v>
       </c>
@@ -2730,8 +3337,20 @@
       <c r="D20" s="5" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E20" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
@@ -2744,9 +3363,20 @@
       <c r="D21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E21" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>75</v>
       </c>
@@ -2759,8 +3389,20 @@
       <c r="D22" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E22" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>79</v>
       </c>
@@ -2773,8 +3415,20 @@
       <c r="D23" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E23" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>83</v>
       </c>
@@ -2787,8 +3441,20 @@
       <c r="D24" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E24" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>87</v>
       </c>
@@ -2798,25 +3464,49 @@
       <c r="C25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="9" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E25" s="20" t="s">
+        <v>511</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>92</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E26" s="22" t="s">
+        <v>512</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>94</v>
       </c>
@@ -2826,11 +3516,23 @@
       <c r="C27" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E27" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>98</v>
       </c>
@@ -2843,12 +3545,24 @@
       <c r="D28" s="5" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E28" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -2857,8 +3571,20 @@
       <c r="D29" s="5" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E29" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>106</v>
       </c>
@@ -2871,8 +3597,20 @@
       <c r="D30" s="5" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E30" s="20" t="s">
+        <v>516</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>109</v>
       </c>
@@ -2885,8 +3623,20 @@
       <c r="D31" s="5" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E31" s="22" t="s">
+        <v>517</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>113</v>
       </c>
@@ -2899,8 +3649,20 @@
       <c r="D32" s="5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E32" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>116</v>
       </c>
@@ -2913,8 +3675,20 @@
       <c r="D33" s="5" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E33" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>120</v>
       </c>
@@ -2927,8 +3701,20 @@
       <c r="D34" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E34" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>124</v>
       </c>
@@ -2941,8 +3727,20 @@
       <c r="D35" s="5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E35" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>127</v>
       </c>
@@ -2955,8 +3753,20 @@
       <c r="D36" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E36" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>130</v>
       </c>
@@ -2969,8 +3779,20 @@
       <c r="D37" s="5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E37" s="22" t="s">
+        <v>522</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>134</v>
       </c>
@@ -2983,8 +3805,20 @@
       <c r="D38" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E38" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>138</v>
       </c>
@@ -2997,8 +3831,20 @@
       <c r="D39" s="5" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E39" s="20" t="s">
+        <v>524</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>142</v>
       </c>
@@ -3011,8 +3857,20 @@
       <c r="D40" s="5" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E40" s="20" t="s">
+        <v>525</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>145</v>
       </c>
@@ -3025,8 +3883,20 @@
       <c r="D41" s="5" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E41" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>148</v>
       </c>
@@ -3039,8 +3909,20 @@
       <c r="D42" s="5" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E42" s="20" t="s">
+        <v>527</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>151</v>
       </c>
@@ -3053,8 +3935,20 @@
       <c r="D43" s="5" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E43" s="20" t="s">
+        <v>528</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>154</v>
       </c>
@@ -3067,8 +3961,20 @@
       <c r="D44" s="5" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E44" s="22" t="s">
+        <v>529</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G44" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>158</v>
       </c>
@@ -3081,8 +3987,20 @@
       <c r="D45" s="5" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E45" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="H45" s="20" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>162</v>
       </c>
@@ -3095,8 +4013,20 @@
       <c r="D46" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E46" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G46" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>165</v>
       </c>
@@ -3109,8 +4039,20 @@
       <c r="D47" s="5" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E47" s="20" t="s">
+        <v>532</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H47" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>169</v>
       </c>
@@ -3123,8 +4065,20 @@
       <c r="D48" s="5" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E48" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H48" s="22" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>172</v>
       </c>
@@ -3134,11 +4088,23 @@
       <c r="C49" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="11" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E49" s="22" t="s">
+        <v>534</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H49" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>176</v>
       </c>
@@ -3151,8 +4117,20 @@
       <c r="D50" s="5" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E50" s="22" t="s">
+        <v>535</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H50" s="22" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>180</v>
       </c>
@@ -3165,8 +4143,20 @@
       <c r="D51" s="5" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E51" s="20" t="s">
+        <v>536</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H51" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>184</v>
       </c>
@@ -3179,8 +4169,20 @@
       <c r="D52" s="5" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E52" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="H52" s="20" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>187</v>
       </c>
@@ -3193,8 +4195,20 @@
       <c r="D53" s="5" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E53" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G53" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H53" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>190</v>
       </c>
@@ -3207,8 +4221,20 @@
       <c r="D54" s="5" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E54" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G54" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H54" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>193</v>
       </c>
@@ -3221,8 +4247,20 @@
       <c r="D55" s="5" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E55" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="H55" s="20" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>196</v>
       </c>
@@ -3235,8 +4273,20 @@
       <c r="D56" s="5" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E56" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="F56" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H56" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>200</v>
       </c>
@@ -3249,8 +4299,20 @@
       <c r="D57" s="5" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E57" s="22" t="s">
+        <v>542</v>
+      </c>
+      <c r="F57" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G57" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H57" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>204</v>
       </c>
@@ -3263,8 +4325,20 @@
       <c r="D58" s="5" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E58" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>207</v>
       </c>
@@ -3277,8 +4351,20 @@
       <c r="D59" s="5" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E59" s="22" t="s">
+        <v>544</v>
+      </c>
+      <c r="F59" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H59" s="22" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>211</v>
       </c>
@@ -3291,8 +4377,20 @@
       <c r="D60" s="5" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E60" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>214</v>
       </c>
@@ -3305,8 +4403,20 @@
       <c r="D61" s="5" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E61" s="22" t="s">
+        <v>546</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>218</v>
       </c>
@@ -3319,8 +4429,20 @@
       <c r="D62" s="5" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E62" s="20" t="s">
+        <v>547</v>
+      </c>
+      <c r="F62" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G62" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>221</v>
       </c>
@@ -3333,8 +4455,20 @@
       <c r="D63" s="5" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E63" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>225</v>
       </c>
@@ -3347,8 +4481,20 @@
       <c r="D64" s="5" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E64" s="20" t="s">
+        <v>549</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G64" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>228</v>
       </c>
@@ -3361,8 +4507,20 @@
       <c r="D65" s="5" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E65" s="20" t="s">
+        <v>550</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>231</v>
       </c>
@@ -3375,8 +4533,20 @@
       <c r="D66" s="5" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E66" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G66" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>234</v>
       </c>
@@ -3389,8 +4559,20 @@
       <c r="D67" s="5" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E67" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G67" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>237</v>
       </c>
@@ -3403,8 +4585,20 @@
       <c r="D68" s="5" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E68" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="F68" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G68" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>240</v>
       </c>
@@ -3417,8 +4611,20 @@
       <c r="D69" s="5" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E69" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="F69" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G69" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H69" s="22" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>244</v>
       </c>
@@ -3431,8 +4637,20 @@
       <c r="D70" s="5" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E70" s="22" t="s">
+        <v>555</v>
+      </c>
+      <c r="F70" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G70" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H70" s="22" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>247</v>
       </c>
@@ -3445,8 +4663,20 @@
       <c r="D71" s="5" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E71" s="20" t="s">
+        <v>556</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H71" s="20" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>250</v>
       </c>
@@ -3459,8 +4689,20 @@
       <c r="D72" s="5" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E72" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="F72" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G72" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="H72" s="20" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>253</v>
       </c>
@@ -3473,8 +4715,20 @@
       <c r="D73" s="5" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E73" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="F73" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="H73" s="20" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>256</v>
       </c>
@@ -3487,8 +4741,20 @@
       <c r="D74" s="5" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E74" s="20" t="s">
+        <v>559</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G74" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="H74" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>259</v>
       </c>
@@ -3501,8 +4767,20 @@
       <c r="D75" s="5" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E75" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H75" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>262</v>
       </c>
@@ -3515,8 +4793,20 @@
       <c r="D76" s="5" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E76" s="22" t="s">
+        <v>561</v>
+      </c>
+      <c r="F76" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="H76" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>265</v>
       </c>
@@ -3529,8 +4819,20 @@
       <c r="D77" s="5" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E77" s="22" t="s">
+        <v>562</v>
+      </c>
+      <c r="F77" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="G77" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H77" s="22" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>269</v>
       </c>
@@ -3543,8 +4845,20 @@
       <c r="D78" s="5" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E78" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="F78" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G78" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="H78" s="20" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>273</v>
       </c>
@@ -3557,18 +4871,30 @@
       <c r="D79" s="5" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E79" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="F79" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G79" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="H79" s="20" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D80" s="16" t="s">
         <v>433</v>
       </c>
     </row>
@@ -3576,13 +4902,13 @@
       <c r="A81" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="16" t="s">
         <v>434</v>
       </c>
     </row>
@@ -3590,13 +4916,13 @@
       <c r="A82" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="16" t="s">
         <v>435</v>
       </c>
     </row>
@@ -3604,13 +4930,13 @@
       <c r="A83" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="16" t="s">
         <v>436</v>
       </c>
     </row>
@@ -3621,10 +4947,10 @@
       <c r="B84" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="16" t="s">
         <v>437</v>
       </c>
     </row>
@@ -3635,10 +4961,10 @@
       <c r="B85" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="16" t="s">
         <v>438</v>
       </c>
     </row>
@@ -3649,10 +4975,10 @@
       <c r="B86" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="16" t="s">
         <v>439</v>
       </c>
     </row>
@@ -3660,13 +4986,13 @@
       <c r="A87" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="16" t="s">
         <v>440</v>
       </c>
     </row>
@@ -3677,10 +5003,10 @@
       <c r="B88" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="D88" s="17" t="s">
+      <c r="D88" s="16" t="s">
         <v>441</v>
       </c>
     </row>
@@ -3688,13 +5014,13 @@
       <c r="A89" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D89" s="17" t="s">
+      <c r="D89" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3705,10 +5031,10 @@
       <c r="B90" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="D90" s="17" t="s">
+      <c r="D90" s="16" t="s">
         <v>442</v>
       </c>
     </row>
@@ -3716,13 +5042,13 @@
       <c r="A91" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C91" s="16" t="s">
+      <c r="C91" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D91" s="17" t="s">
+      <c r="D91" s="16" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3730,13 +5056,13 @@
       <c r="A92" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C92" s="16" t="s">
+      <c r="C92" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D92" s="17" t="s">
+      <c r="D92" s="16" t="s">
         <v>443</v>
       </c>
     </row>
@@ -3744,13 +5070,13 @@
       <c r="A93" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="D93" s="17" t="s">
+      <c r="D93" s="16" t="s">
         <v>444</v>
       </c>
     </row>
@@ -3758,13 +5084,13 @@
       <c r="A94" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D94" s="17" t="s">
+      <c r="D94" s="16" t="s">
         <v>445</v>
       </c>
     </row>
@@ -3772,13 +5098,13 @@
       <c r="A95" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D95" s="16" t="s">
         <v>446</v>
       </c>
     </row>
@@ -3786,13 +5112,13 @@
       <c r="A96" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C96" s="16" t="s">
+      <c r="C96" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D96" s="17" t="s">
+      <c r="D96" s="16" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3806,7 +5132,7 @@
       <c r="C97" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D97" s="17" t="s">
+      <c r="D97" s="16" t="s">
         <v>447</v>
       </c>
     </row>
@@ -3814,13 +5140,13 @@
       <c r="A98" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C98" s="16" t="s">
+      <c r="C98" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D98" s="18" t="s">
+      <c r="D98" s="17" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3828,13 +5154,13 @@
       <c r="A99" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D99" s="17" t="s">
+      <c r="D99" s="16" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3842,13 +5168,13 @@
       <c r="A100" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C100" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="16" t="s">
         <v>448</v>
       </c>
     </row>
@@ -3856,13 +5182,13 @@
       <c r="A101" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="B101" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D101" s="17" t="s">
+      <c r="D101" s="16" t="s">
         <v>449</v>
       </c>
     </row>
@@ -3870,13 +5196,13 @@
       <c r="A102" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D102" s="17" t="s">
+      <c r="D102" s="16" t="s">
         <v>450</v>
       </c>
     </row>
@@ -3884,13 +5210,13 @@
       <c r="A103" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C103" s="13" t="s">
+      <c r="C103" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D103" s="17" t="s">
+      <c r="D103" s="16" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3898,13 +5224,13 @@
       <c r="A104" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B104" s="13" t="s">
+      <c r="B104" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C104" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D104" s="17" t="s">
+      <c r="D104" s="16" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3915,10 +5241,10 @@
       <c r="B105" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="D105" s="17" t="s">
+      <c r="D105" s="16" t="s">
         <v>451</v>
       </c>
     </row>
@@ -3926,13 +5252,13 @@
       <c r="A106" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C106" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D106" s="17" t="s">
+      <c r="D106" s="16" t="s">
         <v>452</v>
       </c>
     </row>
@@ -3943,10 +5269,10 @@
       <c r="B107" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C107" s="13" t="s">
+      <c r="C107" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="D107" s="17" t="s">
+      <c r="D107" s="16" t="s">
         <v>453</v>
       </c>
     </row>
@@ -3957,10 +5283,10 @@
       <c r="B108" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C108" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D108" s="17" t="s">
+      <c r="D108" s="16" t="s">
         <v>454</v>
       </c>
     </row>
@@ -3968,13 +5294,13 @@
       <c r="A109" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="D109" s="17" t="s">
+      <c r="D109" s="16" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3982,13 +5308,13 @@
       <c r="A110" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C110" s="16" t="s">
+      <c r="C110" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D110" s="17" t="s">
+      <c r="D110" s="16" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3996,13 +5322,13 @@
       <c r="A111" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C111" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D111" s="17" t="s">
+      <c r="D111" s="16" t="s">
         <v>455</v>
       </c>
     </row>
@@ -4013,10 +5339,10 @@
       <c r="B112" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C112" s="13" t="s">
+      <c r="C112" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="D112" s="17" t="s">
+      <c r="D112" s="16" t="s">
         <v>456</v>
       </c>
     </row>
@@ -4027,10 +5353,10 @@
       <c r="B113" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C113" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="D113" s="17" t="s">
+      <c r="D113" s="16" t="s">
         <v>457</v>
       </c>
     </row>
@@ -4038,13 +5364,13 @@
       <c r="A114" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D114" s="17" t="s">
+      <c r="D114" s="16" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4052,13 +5378,13 @@
       <c r="A115" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="C115" s="16" t="s">
+      <c r="C115" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="D115" s="17" t="s">
+      <c r="D115" s="16" t="s">
         <v>153</v>
       </c>
     </row>
@@ -4069,10 +5395,10 @@
       <c r="B116" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="D116" s="17" t="s">
+      <c r="D116" s="16" t="s">
         <v>458</v>
       </c>
     </row>
@@ -4080,13 +5406,13 @@
       <c r="A117" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B117" s="13" t="s">
+      <c r="B117" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="D117" s="17" t="s">
+      <c r="D117" s="16" t="s">
         <v>157</v>
       </c>
     </row>
@@ -4097,10 +5423,10 @@
       <c r="B118" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C118" s="15" t="s">
+      <c r="C118" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="D118" s="17" t="s">
+      <c r="D118" s="16" t="s">
         <v>459</v>
       </c>
     </row>
@@ -4111,10 +5437,10 @@
       <c r="B119" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="D119" s="17" t="s">
+      <c r="D119" s="16" t="s">
         <v>460</v>
       </c>
     </row>
@@ -4122,13 +5448,13 @@
       <c r="A120" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="C120" s="16" t="s">
+      <c r="C120" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D120" s="17" t="s">
+      <c r="D120" s="16" t="s">
         <v>171</v>
       </c>
     </row>
@@ -4139,10 +5465,10 @@
       <c r="B121" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C121" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="D121" s="17" t="s">
+      <c r="D121" s="16" t="s">
         <v>461</v>
       </c>
     </row>
@@ -4153,10 +5479,10 @@
       <c r="B122" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="D122" s="17" t="s">
+      <c r="D122" s="16" t="s">
         <v>462</v>
       </c>
     </row>
@@ -4167,10 +5493,10 @@
       <c r="B123" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="D123" s="17" t="s">
+      <c r="D123" s="16" t="s">
         <v>463</v>
       </c>
     </row>
@@ -4181,10 +5507,10 @@
       <c r="B124" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C124" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="D124" s="17" t="s">
+      <c r="D124" s="16" t="s">
         <v>464</v>
       </c>
     </row>
@@ -4192,13 +5518,13 @@
       <c r="A125" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="C125" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="D125" s="17" t="s">
+      <c r="D125" s="16" t="s">
         <v>465</v>
       </c>
     </row>
@@ -4206,13 +5532,13 @@
       <c r="A126" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B126" s="15" t="s">
+      <c r="B126" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="C126" s="13" t="s">
+      <c r="C126" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D126" s="17" t="s">
+      <c r="D126" s="16" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4220,13 +5546,13 @@
       <c r="A127" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B127" s="15" t="s">
+      <c r="B127" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="C127" s="15" t="s">
+      <c r="C127" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D127" s="17" t="s">
+      <c r="D127" s="16" t="s">
         <v>466</v>
       </c>
     </row>
@@ -4234,13 +5560,13 @@
       <c r="A128" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B128" s="15" t="s">
+      <c r="B128" s="14" t="s">
         <v>388</v>
       </c>
-      <c r="C128" s="15" t="s">
+      <c r="C128" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D128" s="17" t="s">
+      <c r="D128" s="16" t="s">
         <v>467</v>
       </c>
     </row>
@@ -4251,10 +5577,10 @@
       <c r="B129" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="C129" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="D129" s="17" t="s">
+      <c r="D129" s="16" t="s">
         <v>468</v>
       </c>
     </row>
@@ -4262,13 +5588,13 @@
       <c r="A130" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B130" s="13" t="s">
+      <c r="B130" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="C130" s="13" t="s">
+      <c r="C130" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D130" s="17" t="s">
+      <c r="D130" s="16" t="s">
         <v>469</v>
       </c>
     </row>
@@ -4276,13 +5602,13 @@
       <c r="A131" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B131" s="13" t="s">
+      <c r="B131" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C131" s="13" t="s">
+      <c r="C131" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="D131" s="17" t="s">
+      <c r="D131" s="16" t="s">
         <v>470</v>
       </c>
     </row>
@@ -4290,13 +5616,13 @@
       <c r="A132" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="B132" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="C132" s="13" t="s">
+      <c r="C132" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="D132" s="17" t="s">
+      <c r="D132" s="16" t="s">
         <v>471</v>
       </c>
     </row>
@@ -4304,13 +5630,13 @@
       <c r="A133" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B133" s="13" t="s">
+      <c r="B133" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="C133" s="13" t="s">
+      <c r="C133" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D133" s="17" t="s">
+      <c r="D133" s="16" t="s">
         <v>472</v>
       </c>
     </row>
@@ -4321,10 +5647,10 @@
       <c r="B134" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C134" s="13" t="s">
+      <c r="C134" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D134" s="17" t="s">
+      <c r="D134" s="16" t="s">
         <v>473</v>
       </c>
     </row>
@@ -4332,13 +5658,13 @@
       <c r="A135" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B135" s="13" t="s">
+      <c r="B135" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="C135" s="13" t="s">
+      <c r="C135" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="D135" s="17" t="s">
+      <c r="D135" s="16" t="s">
         <v>474</v>
       </c>
     </row>
@@ -4349,10 +5675,10 @@
       <c r="B136" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C136" s="13" t="s">
+      <c r="C136" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="D136" s="16" t="s">
         <v>475</v>
       </c>
     </row>
@@ -4360,13 +5686,13 @@
       <c r="A137" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B137" s="13" t="s">
+      <c r="B137" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C137" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="D137" s="17" t="s">
+      <c r="D137" s="16" t="s">
         <v>476</v>
       </c>
     </row>
@@ -4374,13 +5700,13 @@
       <c r="A138" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B138" s="13" t="s">
+      <c r="B138" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="C138" s="13" t="s">
+      <c r="C138" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="D138" s="17" t="s">
+      <c r="D138" s="16" t="s">
         <v>217</v>
       </c>
     </row>
@@ -4388,13 +5714,13 @@
       <c r="A139" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B139" s="13" t="s">
+      <c r="B139" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="C139" s="13" t="s">
+      <c r="C139" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D139" s="17" t="s">
+      <c r="D139" s="16" t="s">
         <v>224</v>
       </c>
     </row>
@@ -4402,13 +5728,13 @@
       <c r="A140" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B140" s="13" t="s">
+      <c r="B140" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="C140" s="13" t="s">
+      <c r="C140" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="D140" s="17" t="s">
+      <c r="D140" s="16" t="s">
         <v>477</v>
       </c>
     </row>
@@ -4419,10 +5745,10 @@
       <c r="B141" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C141" s="13" t="s">
+      <c r="C141" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="D141" s="17" t="s">
+      <c r="D141" s="16" t="s">
         <v>478</v>
       </c>
     </row>
@@ -4430,13 +5756,13 @@
       <c r="A142" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B142" s="13" t="s">
+      <c r="B142" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="C142" s="13" t="s">
+      <c r="C142" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="D142" s="17" t="s">
+      <c r="D142" s="16" t="s">
         <v>479</v>
       </c>
     </row>
@@ -4444,13 +5770,13 @@
       <c r="A143" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B143" s="13" t="s">
+      <c r="B143" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C143" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D143" s="17" t="s">
+      <c r="D143" s="16" t="s">
         <v>480</v>
       </c>
     </row>
@@ -4458,13 +5784,13 @@
       <c r="A144" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B144" s="13" t="s">
+      <c r="B144" s="12" t="s">
         <v>402</v>
       </c>
-      <c r="C144" s="13" t="s">
+      <c r="C144" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D144" s="17" t="s">
+      <c r="D144" s="16" t="s">
         <v>481</v>
       </c>
     </row>
@@ -4475,10 +5801,10 @@
       <c r="B145" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="C145" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D145" s="17" t="s">
+      <c r="D145" s="16" t="s">
         <v>482</v>
       </c>
     </row>
@@ -4486,13 +5812,13 @@
       <c r="A146" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B146" s="13" t="s">
+      <c r="B146" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C146" s="13" t="s">
+      <c r="C146" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D146" s="17" t="s">
+      <c r="D146" s="16" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4500,13 +5826,13 @@
       <c r="A147" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B147" s="13" t="s">
+      <c r="B147" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C147" s="13" t="s">
+      <c r="C147" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D147" s="17" t="s">
+      <c r="D147" s="16" t="s">
         <v>243</v>
       </c>
     </row>
@@ -4514,13 +5840,13 @@
       <c r="A148" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B148" s="13" t="s">
+      <c r="B148" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C148" s="16" t="s">
+      <c r="C148" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D148" s="17" t="s">
+      <c r="D148" s="16" t="s">
         <v>252</v>
       </c>
     </row>
@@ -4528,13 +5854,13 @@
       <c r="A149" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B149" s="13" t="s">
+      <c r="B149" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="C149" s="16" t="s">
+      <c r="C149" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D149" s="17" t="s">
+      <c r="D149" s="16" t="s">
         <v>255</v>
       </c>
     </row>
@@ -4545,10 +5871,10 @@
       <c r="B150" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C150" s="13" t="s">
+      <c r="C150" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D150" s="17" t="s">
+      <c r="D150" s="16" t="s">
         <v>483</v>
       </c>
     </row>
@@ -4556,13 +5882,13 @@
       <c r="A151" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B151" s="13" t="s">
+      <c r="B151" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="C151" s="13" t="s">
+      <c r="C151" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="D151" s="17" t="s">
+      <c r="D151" s="16" t="s">
         <v>484</v>
       </c>
     </row>
@@ -4573,10 +5899,10 @@
       <c r="B152" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C152" s="13" t="s">
+      <c r="C152" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="D152" s="17" t="s">
+      <c r="D152" s="16" t="s">
         <v>485</v>
       </c>
     </row>
@@ -4584,13 +5910,13 @@
       <c r="A153" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B153" s="13" t="s">
+      <c r="B153" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="C153" s="13" t="s">
+      <c r="C153" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="D153" s="17" t="s">
+      <c r="D153" s="16" t="s">
         <v>486</v>
       </c>
     </row>
@@ -4598,13 +5924,13 @@
       <c r="A154" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B154" s="13" t="s">
+      <c r="B154" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="C154" s="13" t="s">
+      <c r="C154" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="D154" s="17" t="s">
+      <c r="D154" s="16" t="s">
         <v>487</v>
       </c>
     </row>

--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website-Project\IKS\iks-digital-repository\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBFA22D-75F5-4BC5-BE2B-1F6A5EB0E28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03E7216-5048-439E-B02A-A61D11F17B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="705">
   <si>
     <t>Voucher No</t>
   </si>
@@ -2374,12 +2374,309 @@
   <si>
     <t>Leaf, seed, fruit</t>
   </si>
+  <si>
+    <t>Muktajhuri</t>
+  </si>
+  <si>
+    <t>Pashanbheda</t>
+  </si>
+  <si>
+    <t>Uchunti</t>
+  </si>
+  <si>
+    <t>Rasun</t>
+  </si>
+  <si>
+    <t>Sankhasaru</t>
+  </si>
+  <si>
+    <t>Chatiana</t>
+  </si>
+  <si>
+    <t>Madaranga</t>
+  </si>
+  <si>
+    <t>Kantasaga</t>
+  </si>
+  <si>
+    <t>Shatavari</t>
+  </si>
+  <si>
+    <t>Siali</t>
+  </si>
+  <si>
+    <t>Pitaboitalu</t>
+  </si>
+  <si>
+    <t>Bhursuni</t>
+  </si>
+  <si>
+    <t>Tal</t>
+  </si>
+  <si>
+    <t>Charakoli</t>
+  </si>
+  <si>
+    <t>Amruta-bhanda</t>
+  </si>
+  <si>
+    <t>Nahinga</t>
+  </si>
+  <si>
+    <t>Pokasunga</t>
+  </si>
+  <si>
+    <t>Bana sorisa</t>
+  </si>
+  <si>
+    <t>Aparajita</t>
+  </si>
+  <si>
+    <t>Surkali</t>
+  </si>
+  <si>
+    <t>Kansira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talamuli </t>
+  </si>
+  <si>
+    <t>Kala gaja</t>
+  </si>
+  <si>
+    <t>Mutha</t>
+  </si>
+  <si>
+    <t>Kuradiagachha</t>
+  </si>
+  <si>
+    <t>Bainga</t>
+  </si>
+  <si>
+    <t>Sarahara</t>
+  </si>
+  <si>
+    <t>Khira saga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kshirasijhu </t>
+  </si>
+  <si>
+    <t>Baidimiri</t>
+  </si>
+  <si>
+    <t>Podehi</t>
+  </si>
+  <si>
+    <t>Panamahuri</t>
+  </si>
+  <si>
+    <t>Gurudukoli</t>
+  </si>
+  <si>
+    <t>Sarsaparilla/ Anantmula</t>
+  </si>
+  <si>
+    <t>PaniJovali</t>
+  </si>
+  <si>
+    <t>Gilleri</t>
+  </si>
+  <si>
+    <t>Dhala bagada</t>
+  </si>
+  <si>
+    <t>Dhala baigaba</t>
+  </si>
+  <si>
+    <t>Laoo</t>
+  </si>
+  <si>
+    <t>Patheri</t>
+  </si>
+  <si>
+    <t>Patri</t>
+  </si>
+  <si>
+    <t>Amba</t>
+  </si>
+  <si>
+    <t>Lajakulilata</t>
+  </si>
+  <si>
+    <t>Kalara</t>
+  </si>
+  <si>
+    <t>Kankad</t>
+  </si>
+  <si>
+    <t>Kala jeera</t>
+  </si>
+  <si>
+    <t>Gangasiuli</t>
+  </si>
+  <si>
+    <t>Tulasi</t>
+  </si>
+  <si>
+    <t>Nagaphana</t>
+  </si>
+  <si>
+    <t>Aanla</t>
+  </si>
+  <si>
+    <t>Bhuiankakharu</t>
+  </si>
+  <si>
+    <t>Aeronda</t>
+  </si>
+  <si>
+    <t>Ban Dhanyavaad</t>
+  </si>
+  <si>
+    <t>Tila/Khasa</t>
+  </si>
+  <si>
+    <t>Sal</t>
+  </si>
+  <si>
+    <t>Soibala</t>
+  </si>
+  <si>
+    <t>Bajramuli</t>
+  </si>
+  <si>
+    <t>Gokari</t>
+  </si>
+  <si>
+    <t>Jhumpuri</t>
+  </si>
+  <si>
+    <t>Jamun</t>
+  </si>
+  <si>
+    <t>Begunia</t>
+  </si>
+  <si>
+    <t>Kesharaj</t>
+  </si>
+  <si>
+    <t>Aswagandha</t>
+  </si>
+  <si>
+    <t>Barkoli</t>
+  </si>
+  <si>
+    <t>Kanteikoli</t>
+  </si>
+  <si>
+    <t>Climber</t>
+  </si>
+  <si>
+    <t>Podanga (Keonjhar)</t>
+  </si>
+  <si>
+    <t>Tenteinali (Keonjhar)</t>
+  </si>
+  <si>
+    <t>Guptaganga (Keonjhar)</t>
+  </si>
+  <si>
+    <t>Bhalujodi (Keonjhar)</t>
+  </si>
+  <si>
+    <t>Rangamatia (Keonjhar)</t>
+  </si>
+  <si>
+    <t>Bulb</t>
+  </si>
+  <si>
+    <t>Tuber and leaf</t>
+  </si>
+  <si>
+    <t>Bark, leaf, latex</t>
+  </si>
+  <si>
+    <t>Leaf, stem and flower</t>
+  </si>
+  <si>
+    <t>Roots, Leaf</t>
+  </si>
+  <si>
+    <t>Lat: 21°69'19472" N Lng: 85°18'93945" E</t>
+  </si>
+  <si>
+    <t>Roots</t>
+  </si>
+  <si>
+    <t>Fruit and leaf</t>
+  </si>
+  <si>
+    <t>Leaf, seed, root</t>
+  </si>
+  <si>
+    <t>Seeds</t>
+  </si>
+  <si>
+    <t>Tuber, Leaf</t>
+  </si>
+  <si>
+    <t>Tuber and Rhizome</t>
+  </si>
+  <si>
+    <t>Laef, stem, root &amp; flower</t>
+  </si>
+  <si>
+    <t>Stem, root, bark</t>
+  </si>
+  <si>
+    <t>Leaf, Bark, Root, Latex</t>
+  </si>
+  <si>
+    <t>Seed, bulb, leaf  flower</t>
+  </si>
+  <si>
+    <t>Leaf and Root</t>
+  </si>
+  <si>
+    <t>Leaf, Bark, Root</t>
+  </si>
+  <si>
+    <t>Tuberous root</t>
+  </si>
+  <si>
+    <t>Seed, leaf, stem, Root</t>
+  </si>
+  <si>
+    <t>Flower. Fruits, Seeds</t>
+  </si>
+  <si>
+    <t>Root, leaf, seed</t>
+  </si>
+  <si>
+    <t>Leaf, flower, seed, bark</t>
+  </si>
+  <si>
+    <t>Stems (cladodes), flowers</t>
+  </si>
+  <si>
+    <t>Fruit, tuber</t>
+  </si>
+  <si>
+    <t>Seed, leaf, root, bark</t>
+  </si>
+  <si>
+    <t>Fruit,Seeds</t>
+  </si>
+  <si>
+    <t>Leaf, flower</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2415,6 +2712,12 @@
     <font>
       <i/>
       <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -2466,7 +2769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2536,6 +2839,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2824,7 +3136,7 @@
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="56.33203125" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.77734375" bestFit="1" customWidth="1"/>
@@ -3350,7 +3662,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
@@ -3480,7 +3792,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>90</v>
       </c>
@@ -4234,7 +4546,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>193</v>
       </c>
@@ -4897,8 +5209,20 @@
       <c r="D80" s="16" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E80" s="21" t="s">
+        <v>606</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G80" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H80" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>278</v>
       </c>
@@ -4911,8 +5235,20 @@
       <c r="D81" s="16" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E81" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G81" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>279</v>
       </c>
@@ -4925,8 +5261,20 @@
       <c r="D82" s="16" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E82" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G82" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H82" s="21" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>280</v>
       </c>
@@ -4939,8 +5287,20 @@
       <c r="D83" s="16" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E83" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="F83" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>281</v>
       </c>
@@ -4953,8 +5313,20 @@
       <c r="D84" s="16" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E84" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="F84" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G84" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H84" s="21" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>282</v>
       </c>
@@ -4967,8 +5339,20 @@
       <c r="D85" s="16" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E85" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="F85" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G85" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H85" s="21" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>283</v>
       </c>
@@ -4981,8 +5365,20 @@
       <c r="D86" s="16" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E86" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="F86" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G86" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>284</v>
       </c>
@@ -4995,8 +5391,20 @@
       <c r="D87" s="16" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E87" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G87" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H87" s="21" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>285</v>
       </c>
@@ -5009,8 +5417,20 @@
       <c r="D88" s="16" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E88" s="21" t="s">
+        <v>613</v>
+      </c>
+      <c r="F88" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G88" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H88" s="21" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>286</v>
       </c>
@@ -5023,8 +5443,20 @@
       <c r="D89" s="16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E89" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="F89" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G89" s="21" t="s">
+        <v>675</v>
+      </c>
+      <c r="H89" s="24" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>287</v>
       </c>
@@ -5037,8 +5469,20 @@
       <c r="D90" s="16" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E90" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="F90" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G90" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H90" s="21" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>288</v>
       </c>
@@ -5051,8 +5495,20 @@
       <c r="D91" s="16" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E91" s="21" t="s">
+        <v>498</v>
+      </c>
+      <c r="F91" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G91" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H91" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>289</v>
       </c>
@@ -5065,8 +5521,20 @@
       <c r="D92" s="16" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E92" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="F92" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G92" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H92" s="21" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>290</v>
       </c>
@@ -5079,8 +5547,20 @@
       <c r="D93" s="16" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E93" s="21" t="s">
+        <v>616</v>
+      </c>
+      <c r="F93" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G93" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H93" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>291</v>
       </c>
@@ -5093,8 +5573,20 @@
       <c r="D94" s="16" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="E94" s="21" t="s">
+        <v>617</v>
+      </c>
+      <c r="F94" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G94" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H94" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>292</v>
       </c>
@@ -5107,8 +5599,20 @@
       <c r="D95" s="16" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E95" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="F95" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G95" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H95" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>293</v>
       </c>
@@ -5121,8 +5625,20 @@
       <c r="D96" s="16" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E96" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="F96" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G96" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H96" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>294</v>
       </c>
@@ -5135,8 +5651,20 @@
       <c r="D97" s="16" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E97" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="F97" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G97" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H97" s="21" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>295</v>
       </c>
@@ -5149,8 +5677,20 @@
       <c r="D98" s="17" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E98" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="F98" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G98" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H98" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>296</v>
       </c>
@@ -5163,8 +5703,20 @@
       <c r="D99" s="16" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E99" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="F99" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G99" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H99" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>297</v>
       </c>
@@ -5177,8 +5729,20 @@
       <c r="D100" s="16" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E100" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="F100" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G100" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H100" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>298</v>
       </c>
@@ -5191,8 +5755,20 @@
       <c r="D101" s="16" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E101" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="F101" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G101" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H101" s="21" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>299</v>
       </c>
@@ -5205,8 +5781,20 @@
       <c r="D102" s="16" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E102" s="21" t="s">
+        <v>624</v>
+      </c>
+      <c r="F102" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G102" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H102" s="21" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>300</v>
       </c>
@@ -5219,8 +5807,20 @@
       <c r="D103" s="16" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E103" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="F103" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G103" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H103" s="21" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>301</v>
       </c>
@@ -5233,8 +5833,20 @@
       <c r="D104" s="16" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E104" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="F104" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G104" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H104" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>302</v>
       </c>
@@ -5247,8 +5859,20 @@
       <c r="D105" s="16" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E105" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="F105" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G105" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H105" s="21" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>303</v>
       </c>
@@ -5261,8 +5885,20 @@
       <c r="D106" s="16" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E106" s="21" t="s">
+        <v>628</v>
+      </c>
+      <c r="F106" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G106" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H106" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>304</v>
       </c>
@@ -5275,8 +5911,20 @@
       <c r="D107" s="16" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E107" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="F107" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G107" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H107" s="21" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>305</v>
       </c>
@@ -5289,8 +5937,20 @@
       <c r="D108" s="16" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E108" s="21" t="s">
+        <v>630</v>
+      </c>
+      <c r="F108" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G108" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H108" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>306</v>
       </c>
@@ -5303,8 +5963,20 @@
       <c r="D109" s="16" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E109" s="21" t="s">
+        <v>631</v>
+      </c>
+      <c r="F109" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G109" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H109" s="21" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>307</v>
       </c>
@@ -5317,8 +5989,20 @@
       <c r="D110" s="16" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E110" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="F110" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G110" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H110" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>308</v>
       </c>
@@ -5331,8 +6015,20 @@
       <c r="D111" s="16" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E111" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="F111" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G111" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H111" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>309</v>
       </c>
@@ -5345,8 +6041,20 @@
       <c r="D112" s="16" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E112" s="21" t="s">
+        <v>633</v>
+      </c>
+      <c r="F112" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G112" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H112" s="21" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>310</v>
       </c>
@@ -5359,8 +6067,20 @@
       <c r="D113" s="16" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E113" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="F113" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="G113" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H113" s="21" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>311</v>
       </c>
@@ -5373,8 +6093,20 @@
       <c r="D114" s="16" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E114" s="21" t="s">
+        <v>635</v>
+      </c>
+      <c r="F114" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G114" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H114" s="21" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>312</v>
       </c>
@@ -5387,8 +6119,20 @@
       <c r="D115" s="16" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E115" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="F115" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G115" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H115" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>313</v>
       </c>
@@ -5401,8 +6145,20 @@
       <c r="D116" s="16" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E116" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="F116" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G116" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H116" s="21" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>314</v>
       </c>
@@ -5415,8 +6171,20 @@
       <c r="D117" s="16" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E117" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="F117" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G117" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H117" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>315</v>
       </c>
@@ -5429,8 +6197,20 @@
       <c r="D118" s="16" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E118" s="25" t="s">
+        <v>639</v>
+      </c>
+      <c r="F118" s="25" t="s">
+        <v>566</v>
+      </c>
+      <c r="G118" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H118" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>316</v>
       </c>
@@ -5443,8 +6223,20 @@
       <c r="D119" s="16" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E119" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="F119" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G119" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H119" s="21" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>317</v>
       </c>
@@ -5457,8 +6249,20 @@
       <c r="D120" s="16" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E120" s="21" t="s">
+        <v>641</v>
+      </c>
+      <c r="F120" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G120" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H120" s="21" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>318</v>
       </c>
@@ -5471,8 +6275,20 @@
       <c r="D121" s="16" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E121" s="21" t="s">
+        <v>642</v>
+      </c>
+      <c r="F121" s="21" t="s">
+        <v>671</v>
+      </c>
+      <c r="G121" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H121" s="21" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>319</v>
       </c>
@@ -5485,8 +6301,20 @@
       <c r="D122" s="16" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E122" s="21" t="s">
+        <v>643</v>
+      </c>
+      <c r="F122" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G122" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H122" s="21" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>320</v>
       </c>
@@ -5499,8 +6327,20 @@
       <c r="D123" s="16" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E123" s="21" t="s">
+        <v>644</v>
+      </c>
+      <c r="F123" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G123" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H123" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>321</v>
       </c>
@@ -5513,8 +6353,20 @@
       <c r="D124" s="16" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E124" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="F124" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G124" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H124" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>322</v>
       </c>
@@ -5527,8 +6379,20 @@
       <c r="D125" s="16" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E125" s="21" t="s">
+        <v>646</v>
+      </c>
+      <c r="F125" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G125" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H125" s="21" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>323</v>
       </c>
@@ -5541,8 +6405,20 @@
       <c r="D126" s="16" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E126" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="F126" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G126" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H126" s="21" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>324</v>
       </c>
@@ -5555,8 +6431,20 @@
       <c r="D127" s="16" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E127" s="21" t="s">
+        <v>647</v>
+      </c>
+      <c r="F127" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G127" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H127" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>325</v>
       </c>
@@ -5569,8 +6457,20 @@
       <c r="D128" s="16" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E128" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="F128" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G128" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H128" s="21" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>326</v>
       </c>
@@ -5583,8 +6483,20 @@
       <c r="D129" s="16" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E129" s="21" t="s">
+        <v>649</v>
+      </c>
+      <c r="F129" s="21" t="s">
+        <v>671</v>
+      </c>
+      <c r="G129" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H129" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>327</v>
       </c>
@@ -5597,8 +6509,20 @@
       <c r="D130" s="16" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E130" s="21" t="s">
+        <v>650</v>
+      </c>
+      <c r="F130" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G130" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H130" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>328</v>
       </c>
@@ -5611,8 +6535,20 @@
       <c r="D131" s="16" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E131" s="21" t="s">
+        <v>651</v>
+      </c>
+      <c r="F131" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G131" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H131" s="21" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>329</v>
       </c>
@@ -5625,8 +6561,20 @@
       <c r="D132" s="16" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E132" s="21" t="s">
+        <v>652</v>
+      </c>
+      <c r="F132" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G132" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H132" s="21" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>330</v>
       </c>
@@ -5639,8 +6587,20 @@
       <c r="D133" s="16" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E133" s="21" t="s">
+        <v>653</v>
+      </c>
+      <c r="F133" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G133" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H133" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>331</v>
       </c>
@@ -5653,8 +6613,20 @@
       <c r="D134" s="16" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E134" s="21" t="s">
+        <v>654</v>
+      </c>
+      <c r="F134" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="G134" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H134" s="26" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>332</v>
       </c>
@@ -5667,8 +6639,20 @@
       <c r="D135" s="16" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E135" s="21" t="s">
+        <v>655</v>
+      </c>
+      <c r="F135" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G135" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H135" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>333</v>
       </c>
@@ -5681,8 +6665,20 @@
       <c r="D136" s="16" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E136" s="21" t="s">
+        <v>656</v>
+      </c>
+      <c r="F136" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G136" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H136" s="21" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>334</v>
       </c>
@@ -5695,8 +6691,20 @@
       <c r="D137" s="16" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E137" s="21" t="s">
+        <v>657</v>
+      </c>
+      <c r="F137" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G137" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H137" s="21" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>335</v>
       </c>
@@ -5709,8 +6717,20 @@
       <c r="D138" s="16" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E138" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="F138" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G138" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H138" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>336</v>
       </c>
@@ -5723,8 +6743,20 @@
       <c r="D139" s="16" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E139" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="F139" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G139" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H139" s="21" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>337</v>
       </c>
@@ -5737,8 +6769,20 @@
       <c r="D140" s="16" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E140" s="21" t="s">
+        <v>658</v>
+      </c>
+      <c r="F140" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G140" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H140" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>338</v>
       </c>
@@ -5751,8 +6795,20 @@
       <c r="D141" s="16" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E141" s="21" t="s">
+        <v>659</v>
+      </c>
+      <c r="F141" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G141" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H141" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>339</v>
       </c>
@@ -5765,8 +6821,20 @@
       <c r="D142" s="16" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E142" s="21" t="s">
+        <v>660</v>
+      </c>
+      <c r="F142" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G142" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H142" s="21" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>340</v>
       </c>
@@ -5779,8 +6847,20 @@
       <c r="D143" s="16" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E143" s="21" t="s">
+        <v>661</v>
+      </c>
+      <c r="F143" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G143" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="H143" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>341</v>
       </c>
@@ -5793,8 +6873,20 @@
       <c r="D144" s="16" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E144" s="21" t="s">
+        <v>662</v>
+      </c>
+      <c r="F144" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G144" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H144" s="21" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>342</v>
       </c>
@@ -5807,8 +6899,20 @@
       <c r="D145" s="16" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E145" s="21" t="s">
+        <v>663</v>
+      </c>
+      <c r="F145" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G145" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H145" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>343</v>
       </c>
@@ -5821,8 +6925,20 @@
       <c r="D146" s="16" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E146" s="21" t="s">
+        <v>664</v>
+      </c>
+      <c r="F146" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G146" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H146" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>344</v>
       </c>
@@ -5835,8 +6951,20 @@
       <c r="D147" s="16" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E147" s="21" t="s">
+        <v>665</v>
+      </c>
+      <c r="F147" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G147" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H147" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>345</v>
       </c>
@@ -5849,8 +6977,20 @@
       <c r="D148" s="16" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E148" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="F148" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G148" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H148" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>346</v>
       </c>
@@ -5863,8 +7003,20 @@
       <c r="D149" s="16" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E149" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="F149" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G149" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H149" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>347</v>
       </c>
@@ -5877,8 +7029,20 @@
       <c r="D150" s="16" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E150" s="21" t="s">
+        <v>666</v>
+      </c>
+      <c r="F150" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G150" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H150" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>348</v>
       </c>
@@ -5891,8 +7055,20 @@
       <c r="D151" s="16" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E151" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="F151" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="G151" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H151" s="21" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>349</v>
       </c>
@@ -5905,8 +7081,20 @@
       <c r="D152" s="16" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="E152" s="21" t="s">
+        <v>668</v>
+      </c>
+      <c r="F152" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G152" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="H152" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>350</v>
       </c>
@@ -5919,8 +7107,20 @@
       <c r="D153" s="16" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E153" s="21" t="s">
+        <v>669</v>
+      </c>
+      <c r="F153" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="G153" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H153" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>351</v>
       </c>
@@ -5932,6 +7132,18 @@
       </c>
       <c r="D154" s="16" t="s">
         <v>487</v>
+      </c>
+      <c r="E154" s="21" t="s">
+        <v>670</v>
+      </c>
+      <c r="F154" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="G154" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="H154" s="21" t="s">
+        <v>596</v>
       </c>
     </row>
   </sheetData>

--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website-Project\IKS\iks-digital-repository\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8C44A5-96D7-43D3-83C1-6CFD61A6EBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619149C9-9531-4D1E-9712-B32B587AC8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2511,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -6518,7 +6518,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website-Project\IKS\iks-digital-repository\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619149C9-9531-4D1E-9712-B32B587AC8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC7B821-DA01-4E85-8F9C-C7E88ACCC166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2511,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -6518,11 +6518,11 @@
         <v>174</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I154" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I156" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website-Project\IKS\iks-digital-repository\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC7B821-DA01-4E85-8F9C-C7E88ACCC166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD43DCF6-A42B-47A9-9411-BE2689F95037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="865">
   <si>
     <t>Voucher No</t>
   </si>
@@ -2135,19 +2135,602 @@
   </si>
   <si>
     <t>Kanteikoli</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/76</t>
+  </si>
+  <si>
+    <t>Wedelia chinensis</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/77</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/78</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/79</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/80</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/81</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/82</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/83</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/84</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/85</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/86</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/87</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/88</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/89</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/90</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/91</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/92</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/93</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/94</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/95</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/96</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/97</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/98</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/99</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/100</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/101</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/102</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/103</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/104</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/105</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/106</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/107</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/108</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/109</t>
+  </si>
+  <si>
+    <t>Brassica rapa</t>
+  </si>
+  <si>
+    <t>Angelonia salicariifolia</t>
+  </si>
+  <si>
+    <t>Ouret lanata</t>
+  </si>
+  <si>
+    <t>Barleria cristata</t>
+  </si>
+  <si>
+    <t>Achyranthes aspera L.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Aegle marmelos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (L.) Corr.</t>
+    </r>
+  </si>
+  <si>
+    <t>Anacardium occidentale L</t>
+  </si>
+  <si>
+    <t>Piper longum</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rauwolfia serpentine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (L.) Benth.ex. Kurz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Zingiber officinale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Rosc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Morinda tinctoria </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Roxb.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Operculina turpethum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Linn) Silva Manso</t>
+    </r>
+  </si>
+  <si>
+    <t>Centella asiatica</t>
+  </si>
+  <si>
+    <t>Gymnema sylvestre</t>
+  </si>
+  <si>
+    <t>Eclipta prostrata</t>
+  </si>
+  <si>
+    <t>Gloriosa superba</t>
+  </si>
+  <si>
+    <t>Phyllodium pulchellum</t>
+  </si>
+  <si>
+    <t>Pterospermum acerifolium</t>
+  </si>
+  <si>
+    <t>Cissus quadrangularis</t>
+  </si>
+  <si>
+    <t>Clerodendrum serratum</t>
+  </si>
+  <si>
+    <t>Zingiber zerumbet</t>
+  </si>
+  <si>
+    <t>Antigonon leptopus</t>
+  </si>
+  <si>
+    <t>Combretum indicum</t>
+  </si>
+  <si>
+    <t>Tithonia diversifolia</t>
+  </si>
+  <si>
+    <t>Passiflora racemosa</t>
+  </si>
+  <si>
+    <t>Alternanthera philoxeroides</t>
+  </si>
+  <si>
+    <t>Abutilon indicum</t>
+  </si>
+  <si>
+    <t>Sida cordata</t>
+  </si>
+  <si>
+    <t>Crotalaria retusa</t>
+  </si>
+  <si>
+    <t>Ocimum tenuiflorum</t>
+  </si>
+  <si>
+    <t>Coccinia grandis</t>
+  </si>
+  <si>
+    <t>Mazus pumilus</t>
+  </si>
+  <si>
+    <t>Brassicaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantaginaceae </t>
+  </si>
+  <si>
+    <t>Acanthaceae</t>
+  </si>
+  <si>
+    <t>Amranthaceae</t>
+  </si>
+  <si>
+    <t>Rutaceae</t>
+  </si>
+  <si>
+    <t>Piperaceae</t>
+  </si>
+  <si>
+    <t>Aaapocynaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convolvulaceae </t>
+  </si>
+  <si>
+    <t>Colchicaceae</t>
+  </si>
+  <si>
+    <t>Vitaceae</t>
+  </si>
+  <si>
+    <t>Polygonaceae</t>
+  </si>
+  <si>
+    <t>Passifloraceae</t>
+  </si>
+  <si>
+    <t>Mazaceae</t>
+  </si>
+  <si>
+    <t>It is used to treat skin disorders, liver diseases, promote hair growth</t>
+  </si>
+  <si>
+    <t>It is used to treat inflammation, digestive disorders, respiratory issues</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory properties</t>
+  </si>
+  <si>
+    <t>It is traditionally used for kidney stones treatment</t>
+  </si>
+  <si>
+    <t>It is used to treat cough, inflammatory conditions, anemia, snakebites</t>
+  </si>
+  <si>
+    <t>It is used for Cough, Asthma, Bronchitis</t>
+  </si>
+  <si>
+    <t>It is used for treatment of Indigestion, Cough,  Filarisis and Fever</t>
+  </si>
+  <si>
+    <t>It is used to Preventing hair loss and Skin disease</t>
+  </si>
+  <si>
+    <t>It is used for treating inflammation, Gynaec issues, Diarrhoea, Jaundice, Asthma and Sinusitis</t>
+  </si>
+  <si>
+    <t>It is used to treat Snakebite, High B.P</t>
+  </si>
+  <si>
+    <t>It is used for Flatulence, Anorxia, Colic Hiccup, Piles and Vomitting.</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antibacterial, and antioxidant properties, with extensive traditional use in treating arthritis, wounds, and diabetes</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, hepatoprotective, and anthelmintic properties</t>
+  </si>
+  <si>
+    <t>It has wound-healing, anti-inflammatory, and neuroprotective properties</t>
+  </si>
+  <si>
+    <t>It is used to treat conditions like diabetes, obesity, and snakebites</t>
+  </si>
+  <si>
+    <t>It is used to promote hair growth, reduce premature graying, protect liver and skins</t>
+  </si>
+  <si>
+    <t>It is used to treating arthritis, inflammation, skin diseases, and parasitic infections</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, analgesic, anti-diarrheal, and antioxidant properties</t>
+  </si>
+  <si>
+    <t>It is used to treat inflammation, respiratory issues, skin diseases, and bleeding disorders</t>
+  </si>
+  <si>
+    <t>It is used for helping bone fracture healing, bone mineral density, and treating osteoporosis</t>
+  </si>
+  <si>
+    <t>It is used primarily for treating respiratory ailments, fever, and inflammatory conditions</t>
+  </si>
+  <si>
+    <t>It is used to treat digestive issues, fever, joint pain, skin conditions</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, analgesic, and antioxidant properties</t>
+  </si>
+  <si>
+    <t>It is used to treat diarrhea, fever, skin infections, coughs, and pain</t>
+  </si>
+  <si>
+    <t>It has antimalarial, antidiabetic, anti-inflammatory, and antimicrobial properties</t>
+  </si>
+  <si>
+    <t>It has sedative, anxiolytic and anti-inflammatory properties</t>
+  </si>
+  <si>
+    <t>It has antioxidant, anti-inflammatory, antimicrobial, and anti-tumor properties</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, analgesic, laxative, and demulcent properties</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antioxidant, and wound-healing properties</t>
+  </si>
+  <si>
+    <t>It has antimicrobial, anti-inflammatory, and antinociceptive properties</t>
+  </si>
+  <si>
+    <t>It is used for treatment of anxiety, inflammation, microbial infection</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antioxidant, antimicrobial, and hepatoprotective properties</t>
+  </si>
+  <si>
+    <t>It has antidiabetic, anti-inflammatory, antioxidant, and antimicrobial properties</t>
+  </si>
+  <si>
+    <t>It has anti-nociceptive, antioxidant, and hepatoprotective properties</t>
+  </si>
+  <si>
+    <t>Bhrungaraj</t>
+  </si>
+  <si>
+    <t>Sorisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willowleaf </t>
+  </si>
+  <si>
+    <t>Paunshia</t>
+  </si>
+  <si>
+    <t>Daskerenta</t>
+  </si>
+  <si>
+    <t>Apamaraga</t>
+  </si>
+  <si>
+    <t>Bela</t>
+  </si>
+  <si>
+    <t>Kaju badam</t>
+  </si>
+  <si>
+    <t>Pippali</t>
+  </si>
+  <si>
+    <t>Patalagaruda</t>
+  </si>
+  <si>
+    <t>Adaa</t>
+  </si>
+  <si>
+    <t>Aachu</t>
+  </si>
+  <si>
+    <t>Tihudi</t>
+  </si>
+  <si>
+    <t>Thalkudi</t>
+  </si>
+  <si>
+    <t>Gurmar</t>
+  </si>
+  <si>
+    <t>Kesha bardhini</t>
+  </si>
+  <si>
+    <t>Kalihari</t>
+  </si>
+  <si>
+    <t>Salaparni</t>
+  </si>
+  <si>
+    <t>Kanaka Champa</t>
+  </si>
+  <si>
+    <t>Had Jodi</t>
+  </si>
+  <si>
+    <t>Brahmajasti</t>
+  </si>
+  <si>
+    <t>Parasu Kedar</t>
+  </si>
+  <si>
+    <t>Snehalata</t>
+  </si>
+  <si>
+    <t>Madhumalati</t>
+  </si>
+  <si>
+    <t>Bana suryamukhi</t>
+  </si>
+  <si>
+    <t>Radhatamal</t>
+  </si>
+  <si>
+    <t>Bana Madaranga</t>
+  </si>
+  <si>
+    <t>Pedipedika</t>
+  </si>
+  <si>
+    <t>Bisiripi</t>
+  </si>
+  <si>
+    <t>Chhanapata</t>
+  </si>
+  <si>
+    <t>Nahanga Saga</t>
+  </si>
+  <si>
+    <t>Kunduri</t>
+  </si>
+  <si>
+    <t>Sada Jhinku Phula</t>
+  </si>
+  <si>
+    <t>Root, leaf, flower</t>
+  </si>
+  <si>
+    <t>Root</t>
+  </si>
+  <si>
+    <t>Leaf, bark</t>
+  </si>
+  <si>
+    <t>Roots, stem bark</t>
+  </si>
+  <si>
+    <t>Leaf, root, stem</t>
+  </si>
+  <si>
+    <t>Tuber, Seed</t>
+  </si>
+  <si>
+    <t>Leaf, bark, flower</t>
+  </si>
+  <si>
+    <t>Leaf, stem</t>
+  </si>
+  <si>
+    <t>Root, Stem</t>
+  </si>
+  <si>
+    <t>Seed, fruit, root, leaf</t>
+  </si>
+  <si>
+    <t>Leaf, Stem</t>
+  </si>
+  <si>
+    <t>Leaf, root</t>
+  </si>
+  <si>
+    <t>Flower, seed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2167,14 +2750,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{123BCF32-E1EE-4C70-BA52-E6D6A12AAB37}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -2511,10 +3096,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H157"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H188"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="145.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2540,7 +3135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2566,7 +3161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2592,7 +3187,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -2618,7 +3213,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -2644,7 +3239,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2670,7 +3265,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -2696,7 +3291,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -2722,7 +3317,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -2748,7 +3343,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -2774,7 +3369,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -2800,7 +3395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -2826,7 +3421,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>75</v>
       </c>
@@ -2852,7 +3447,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -2878,7 +3473,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -2904,7 +3499,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -2930,7 +3525,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -2956,7 +3551,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>104</v>
       </c>
@@ -2982,7 +3577,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>108</v>
       </c>
@@ -3008,7 +3603,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>112</v>
       </c>
@@ -3034,7 +3629,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>116</v>
       </c>
@@ -3060,7 +3655,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>121</v>
       </c>
@@ -3086,7 +3681,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>126</v>
       </c>
@@ -3112,7 +3707,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -3138,7 +3733,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -3164,7 +3759,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>141</v>
       </c>
@@ -3190,7 +3785,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>147</v>
       </c>
@@ -3216,7 +3811,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>153</v>
       </c>
@@ -3242,7 +3837,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>159</v>
       </c>
@@ -3268,7 +3863,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>165</v>
       </c>
@@ -3294,7 +3889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>169</v>
       </c>
@@ -3320,7 +3915,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>175</v>
       </c>
@@ -3346,7 +3941,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -3372,7 +3967,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>185</v>
       </c>
@@ -3398,7 +3993,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>190</v>
       </c>
@@ -3424,7 +4019,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>194</v>
       </c>
@@ -3450,7 +4045,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>197</v>
       </c>
@@ -3476,7 +4071,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>202</v>
       </c>
@@ -3502,7 +4097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>207</v>
       </c>
@@ -3528,7 +4123,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>212</v>
       </c>
@@ -3554,7 +4149,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>217</v>
       </c>
@@ -3580,7 +4175,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>221</v>
       </c>
@@ -3606,7 +4201,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>225</v>
       </c>
@@ -3632,7 +4227,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>229</v>
       </c>
@@ -3658,7 +4253,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>234</v>
       </c>
@@ -3684,7 +4279,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>240</v>
       </c>
@@ -3710,7 +4305,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>244</v>
       </c>
@@ -3736,7 +4331,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>249</v>
       </c>
@@ -3762,7 +4357,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>253</v>
       </c>
@@ -3788,7 +4383,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>258</v>
       </c>
@@ -3814,7 +4409,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>264</v>
       </c>
@@ -3840,7 +4435,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>269</v>
       </c>
@@ -3866,7 +4461,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>274</v>
       </c>
@@ -3892,7 +4487,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>278</v>
       </c>
@@ -3918,7 +4513,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>282</v>
       </c>
@@ -3944,7 +4539,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>287</v>
       </c>
@@ -3970,7 +4565,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>292</v>
       </c>
@@ -3996,7 +4591,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>297</v>
       </c>
@@ -4022,7 +4617,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>301</v>
       </c>
@@ -4048,7 +4643,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>306</v>
       </c>
@@ -4074,7 +4669,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>310</v>
       </c>
@@ -4100,7 +4695,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>315</v>
       </c>
@@ -4126,7 +4721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>319</v>
       </c>
@@ -4152,7 +4747,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>325</v>
       </c>
@@ -4178,7 +4773,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>329</v>
       </c>
@@ -4204,7 +4799,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>333</v>
       </c>
@@ -4230,7 +4825,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>338</v>
       </c>
@@ -4256,7 +4851,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>342</v>
       </c>
@@ -4282,7 +4877,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>346</v>
       </c>
@@ -4308,7 +4903,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>351</v>
       </c>
@@ -4334,7 +4929,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>356</v>
       </c>
@@ -4360,7 +4955,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>360</v>
       </c>
@@ -4386,7 +4981,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>364</v>
       </c>
@@ -4412,7 +5007,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>368</v>
       </c>
@@ -4438,7 +5033,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>372</v>
       </c>
@@ -4464,7 +5059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>376</v>
       </c>
@@ -4490,7 +5085,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>380</v>
       </c>
@@ -4516,7 +5111,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>385</v>
       </c>
@@ -4542,7 +5137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>390</v>
       </c>
@@ -4568,7 +5163,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>395</v>
       </c>
@@ -4594,7 +5189,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>401</v>
       </c>
@@ -4620,7 +5215,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>407</v>
       </c>
@@ -4646,7 +5241,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>412</v>
       </c>
@@ -4672,7 +5267,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>414</v>
       </c>
@@ -4698,7 +5293,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>420</v>
       </c>
@@ -4724,7 +5319,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>426</v>
       </c>
@@ -4750,7 +5345,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>432</v>
       </c>
@@ -4776,7 +5371,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>437</v>
       </c>
@@ -4802,7 +5397,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>442</v>
       </c>
@@ -4828,7 +5423,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>445</v>
       </c>
@@ -4854,7 +5449,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>450</v>
       </c>
@@ -4880,7 +5475,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>451</v>
       </c>
@@ -4906,7 +5501,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>456</v>
       </c>
@@ -4932,7 +5527,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>461</v>
       </c>
@@ -4958,7 +5553,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>465</v>
       </c>
@@ -4984,7 +5579,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>470</v>
       </c>
@@ -5010,7 +5605,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>472</v>
       </c>
@@ -5036,7 +5631,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>478</v>
       </c>
@@ -5062,7 +5657,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>479</v>
       </c>
@@ -5088,7 +5683,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>481</v>
       </c>
@@ -5114,7 +5709,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>485</v>
       </c>
@@ -5140,7 +5735,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>490</v>
       </c>
@@ -5166,7 +5761,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>495</v>
       </c>
@@ -5192,7 +5787,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>498</v>
       </c>
@@ -5218,7 +5813,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>500</v>
       </c>
@@ -5244,7 +5839,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>505</v>
       </c>
@@ -5270,7 +5865,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>509</v>
       </c>
@@ -5296,7 +5891,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>515</v>
       </c>
@@ -5322,7 +5917,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>519</v>
       </c>
@@ -5348,7 +5943,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>521</v>
       </c>
@@ -5374,7 +5969,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>522</v>
       </c>
@@ -5400,7 +5995,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>526</v>
       </c>
@@ -5426,7 +6021,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>531</v>
       </c>
@@ -5452,7 +6047,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>536</v>
       </c>
@@ -5478,7 +6073,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>540</v>
       </c>
@@ -5504,7 +6099,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>543</v>
       </c>
@@ -5530,7 +6125,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>549</v>
       </c>
@@ -5556,7 +6151,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>551</v>
       </c>
@@ -5582,7 +6177,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>556</v>
       </c>
@@ -5608,7 +6203,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>561</v>
       </c>
@@ -5634,7 +6229,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>564</v>
       </c>
@@ -5660,7 +6255,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>571</v>
       </c>
@@ -5686,7 +6281,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>575</v>
       </c>
@@ -5712,7 +6307,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>580</v>
       </c>
@@ -5738,7 +6333,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>585</v>
       </c>
@@ -5764,7 +6359,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>591</v>
       </c>
@@ -5790,7 +6385,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>593</v>
       </c>
@@ -5816,7 +6411,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>597</v>
       </c>
@@ -5842,7 +6437,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>602</v>
       </c>
@@ -5868,7 +6463,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>606</v>
       </c>
@@ -5894,7 +6489,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>610</v>
       </c>
@@ -5920,7 +6515,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>615</v>
       </c>
@@ -5946,7 +6541,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>621</v>
       </c>
@@ -5972,7 +6567,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>625</v>
       </c>
@@ -5998,7 +6593,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>630</v>
       </c>
@@ -6024,7 +6619,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>635</v>
       </c>
@@ -6050,7 +6645,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>640</v>
       </c>
@@ -6076,7 +6671,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>645</v>
       </c>
@@ -6102,7 +6697,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>646</v>
       </c>
@@ -6128,7 +6723,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>647</v>
       </c>
@@ -6154,7 +6749,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>652</v>
       </c>
@@ -6180,7 +6775,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>657</v>
       </c>
@@ -6206,7 +6801,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>663</v>
       </c>
@@ -6232,7 +6827,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>667</v>
       </c>
@@ -6258,7 +6853,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>671</v>
       </c>
@@ -6284,7 +6879,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>675</v>
       </c>
@@ -6310,7 +6905,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>677</v>
       </c>
@@ -6336,7 +6931,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>679</v>
       </c>
@@ -6362,7 +6957,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>680</v>
       </c>
@@ -6388,7 +6983,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>681</v>
       </c>
@@ -6414,7 +7009,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>685</v>
       </c>
@@ -6440,7 +7035,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>691</v>
       </c>
@@ -6466,7 +7061,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>696</v>
       </c>
@@ -6492,7 +7087,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>701</v>
       </c>
@@ -6518,11 +7113,882 @@
         <v>174</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>705</v>
+      </c>
+      <c r="B155" t="s">
+        <v>706</v>
+      </c>
+      <c r="C155" t="s">
+        <v>687</v>
+      </c>
+      <c r="D155" t="s">
+        <v>785</v>
+      </c>
+      <c r="E155" t="s">
+        <v>819</v>
+      </c>
+      <c r="F155" t="s">
+        <v>29</v>
+      </c>
+      <c r="G155" t="s">
+        <v>411</v>
+      </c>
+      <c r="H155" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>707</v>
+      </c>
+      <c r="B156" t="s">
+        <v>740</v>
+      </c>
+      <c r="C156" t="s">
+        <v>772</v>
+      </c>
+      <c r="D156" t="s">
+        <v>786</v>
+      </c>
+      <c r="E156" t="s">
+        <v>820</v>
+      </c>
+      <c r="F156" t="s">
+        <v>29</v>
+      </c>
+      <c r="G156" t="s">
+        <v>400</v>
+      </c>
+      <c r="H156" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>708</v>
+      </c>
+      <c r="B157" t="s">
+        <v>741</v>
+      </c>
+      <c r="C157" t="s">
+        <v>773</v>
+      </c>
+      <c r="D157" t="s">
+        <v>787</v>
+      </c>
+      <c r="E157" t="s">
+        <v>821</v>
+      </c>
+      <c r="F157" t="s">
+        <v>29</v>
+      </c>
+      <c r="G157" t="s">
+        <v>411</v>
+      </c>
+      <c r="H157" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>709</v>
+      </c>
+      <c r="B158" t="s">
+        <v>742</v>
+      </c>
+      <c r="C158" t="s">
+        <v>403</v>
+      </c>
+      <c r="D158" t="s">
+        <v>788</v>
+      </c>
+      <c r="E158" t="s">
+        <v>822</v>
+      </c>
+      <c r="F158" t="s">
+        <v>29</v>
+      </c>
+      <c r="G158" t="s">
+        <v>406</v>
+      </c>
+      <c r="H158" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>710</v>
+      </c>
+      <c r="B159" t="s">
+        <v>743</v>
+      </c>
+      <c r="C159" t="s">
+        <v>774</v>
+      </c>
+      <c r="D159" t="s">
+        <v>789</v>
+      </c>
+      <c r="E159" t="s">
+        <v>823</v>
+      </c>
+      <c r="F159" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" t="s">
+        <v>411</v>
+      </c>
+      <c r="H159" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>711</v>
+      </c>
+      <c r="B160" t="s">
+        <v>744</v>
+      </c>
+      <c r="C160" t="s">
+        <v>775</v>
+      </c>
+      <c r="D160" t="s">
+        <v>790</v>
+      </c>
+      <c r="E160" t="s">
+        <v>824</v>
+      </c>
+      <c r="F160" t="s">
+        <v>29</v>
+      </c>
+      <c r="G160" t="s">
+        <v>400</v>
+      </c>
+      <c r="H160" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>712</v>
+      </c>
+      <c r="B161" t="s">
+        <v>745</v>
+      </c>
+      <c r="C161" t="s">
+        <v>776</v>
+      </c>
+      <c r="D161" t="s">
+        <v>791</v>
+      </c>
+      <c r="E161" t="s">
+        <v>825</v>
+      </c>
+      <c r="F161" t="s">
+        <v>21</v>
+      </c>
+      <c r="G161" t="s">
+        <v>406</v>
+      </c>
+      <c r="H161" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>713</v>
+      </c>
+      <c r="B162" t="s">
+        <v>746</v>
+      </c>
+      <c r="C162" t="s">
+        <v>83</v>
+      </c>
+      <c r="D162" t="s">
+        <v>792</v>
+      </c>
+      <c r="E162" t="s">
+        <v>826</v>
+      </c>
+      <c r="F162" t="s">
+        <v>21</v>
+      </c>
+      <c r="G162" t="s">
+        <v>411</v>
+      </c>
+      <c r="H162" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>714</v>
+      </c>
+      <c r="B163" t="s">
+        <v>747</v>
+      </c>
+      <c r="C163" t="s">
+        <v>777</v>
+      </c>
+      <c r="D163" t="s">
+        <v>793</v>
+      </c>
+      <c r="E163" t="s">
+        <v>827</v>
+      </c>
+      <c r="F163" t="s">
+        <v>29</v>
+      </c>
+      <c r="G163" t="s">
+        <v>406</v>
+      </c>
+      <c r="H163" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>715</v>
+      </c>
+      <c r="B164" t="s">
+        <v>748</v>
+      </c>
+      <c r="C164" t="s">
+        <v>778</v>
+      </c>
+      <c r="D164" t="s">
+        <v>794</v>
+      </c>
+      <c r="E164" t="s">
+        <v>828</v>
+      </c>
+      <c r="F164" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" t="s">
+        <v>406</v>
+      </c>
+      <c r="H164" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>716</v>
+      </c>
+      <c r="B165" t="s">
+        <v>749</v>
+      </c>
+      <c r="C165" t="s">
+        <v>161</v>
+      </c>
+      <c r="D165" t="s">
+        <v>795</v>
+      </c>
+      <c r="E165" t="s">
+        <v>829</v>
+      </c>
+      <c r="F165" t="s">
+        <v>29</v>
+      </c>
+      <c r="G165" t="s">
+        <v>455</v>
+      </c>
+      <c r="H165" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>717</v>
+      </c>
+      <c r="B166" t="s">
+        <v>750</v>
+      </c>
+      <c r="C166" t="s">
+        <v>236</v>
+      </c>
+      <c r="D166" t="s">
+        <v>796</v>
+      </c>
+      <c r="E166" t="s">
+        <v>830</v>
+      </c>
+      <c r="F166" t="s">
+        <v>21</v>
+      </c>
+      <c r="G166" t="s">
+        <v>400</v>
+      </c>
+      <c r="H166" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>718</v>
+      </c>
+      <c r="B167" t="s">
+        <v>751</v>
+      </c>
+      <c r="C167" t="s">
+        <v>779</v>
+      </c>
+      <c r="D167" t="s">
+        <v>797</v>
+      </c>
+      <c r="E167" t="s">
+        <v>831</v>
+      </c>
+      <c r="F167" t="s">
+        <v>29</v>
+      </c>
+      <c r="G167" t="s">
+        <v>406</v>
+      </c>
+      <c r="H167" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>719</v>
+      </c>
+      <c r="B168" t="s">
+        <v>752</v>
+      </c>
+      <c r="C168" t="s">
+        <v>545</v>
+      </c>
+      <c r="D168" t="s">
+        <v>798</v>
+      </c>
+      <c r="E168" t="s">
+        <v>832</v>
+      </c>
+      <c r="F168" t="s">
+        <v>29</v>
+      </c>
+      <c r="G168" t="s">
+        <v>411</v>
+      </c>
+      <c r="H168" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>720</v>
+      </c>
+      <c r="B169" t="s">
+        <v>753</v>
+      </c>
+      <c r="C169" t="s">
+        <v>428</v>
+      </c>
+      <c r="D169" t="s">
+        <v>799</v>
+      </c>
+      <c r="E169" t="s">
+        <v>833</v>
+      </c>
+      <c r="F169" t="s">
+        <v>29</v>
+      </c>
+      <c r="G169" t="s">
+        <v>455</v>
+      </c>
+      <c r="H169" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>721</v>
+      </c>
+      <c r="B170" t="s">
+        <v>754</v>
+      </c>
+      <c r="C170" t="s">
+        <v>687</v>
+      </c>
+      <c r="D170" t="s">
+        <v>800</v>
+      </c>
+      <c r="E170" t="s">
+        <v>834</v>
+      </c>
+      <c r="F170" t="s">
+        <v>29</v>
+      </c>
+      <c r="G170" t="s">
+        <v>400</v>
+      </c>
+      <c r="H170" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>722</v>
+      </c>
+      <c r="B171" t="s">
+        <v>755</v>
+      </c>
+      <c r="C171" t="s">
+        <v>780</v>
+      </c>
+      <c r="D171" t="s">
+        <v>801</v>
+      </c>
+      <c r="E171" t="s">
+        <v>835</v>
+      </c>
+      <c r="F171" t="s">
+        <v>29</v>
+      </c>
+      <c r="G171" t="s">
+        <v>406</v>
+      </c>
+      <c r="H171" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>723</v>
+      </c>
+      <c r="B172" t="s">
+        <v>756</v>
+      </c>
+      <c r="C172" t="s">
+        <v>18</v>
+      </c>
+      <c r="D172" t="s">
+        <v>802</v>
+      </c>
+      <c r="E172" t="s">
+        <v>836</v>
+      </c>
+      <c r="F172" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" t="s">
+        <v>411</v>
+      </c>
+      <c r="H172" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>724</v>
+      </c>
+      <c r="B173" t="s">
+        <v>757</v>
+      </c>
+      <c r="C173" t="s">
+        <v>77</v>
+      </c>
+      <c r="D173" t="s">
+        <v>803</v>
+      </c>
+      <c r="E173" t="s">
+        <v>837</v>
+      </c>
+      <c r="F173" t="s">
+        <v>21</v>
+      </c>
+      <c r="G173" t="s">
+        <v>406</v>
+      </c>
+      <c r="H173" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>725</v>
+      </c>
+      <c r="B174" t="s">
+        <v>758</v>
+      </c>
+      <c r="C174" t="s">
+        <v>781</v>
+      </c>
+      <c r="D174" t="s">
+        <v>804</v>
+      </c>
+      <c r="E174" t="s">
+        <v>838</v>
+      </c>
+      <c r="F174" t="s">
+        <v>29</v>
+      </c>
+      <c r="G174" t="s">
+        <v>455</v>
+      </c>
+      <c r="H174" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>726</v>
+      </c>
+      <c r="B175" t="s">
+        <v>759</v>
+      </c>
+      <c r="C175" t="s">
+        <v>255</v>
+      </c>
+      <c r="D175" t="s">
+        <v>805</v>
+      </c>
+      <c r="E175" t="s">
+        <v>839</v>
+      </c>
+      <c r="F175" t="s">
+        <v>13</v>
+      </c>
+      <c r="G175" t="s">
+        <v>455</v>
+      </c>
+      <c r="H175" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>727</v>
+      </c>
+      <c r="B176" t="s">
+        <v>760</v>
+      </c>
+      <c r="C176" t="s">
+        <v>161</v>
+      </c>
+      <c r="D176" t="s">
+        <v>806</v>
+      </c>
+      <c r="E176" t="s">
+        <v>840</v>
+      </c>
+      <c r="F176" t="s">
+        <v>29</v>
+      </c>
+      <c r="G176" t="s">
+        <v>411</v>
+      </c>
+      <c r="H176" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>728</v>
+      </c>
+      <c r="B177" t="s">
+        <v>761</v>
+      </c>
+      <c r="C177" t="s">
+        <v>782</v>
+      </c>
+      <c r="D177" t="s">
+        <v>807</v>
+      </c>
+      <c r="E177" t="s">
+        <v>841</v>
+      </c>
+      <c r="F177" t="s">
+        <v>569</v>
+      </c>
+      <c r="G177" t="s">
+        <v>406</v>
+      </c>
+      <c r="H177" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>729</v>
+      </c>
+      <c r="B178" t="s">
+        <v>762</v>
+      </c>
+      <c r="C178" t="s">
+        <v>44</v>
+      </c>
+      <c r="D178" t="s">
+        <v>808</v>
+      </c>
+      <c r="E178" t="s">
+        <v>842</v>
+      </c>
+      <c r="F178" t="s">
+        <v>569</v>
+      </c>
+      <c r="G178" t="s">
+        <v>406</v>
+      </c>
+      <c r="H178" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>730</v>
+      </c>
+      <c r="B179" t="s">
+        <v>763</v>
+      </c>
+      <c r="C179" t="s">
+        <v>687</v>
+      </c>
+      <c r="D179" t="s">
+        <v>809</v>
+      </c>
+      <c r="E179" t="s">
+        <v>843</v>
+      </c>
+      <c r="F179" t="s">
+        <v>29</v>
+      </c>
+      <c r="G179" t="s">
+        <v>455</v>
+      </c>
+      <c r="H179" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>731</v>
+      </c>
+      <c r="B180" t="s">
+        <v>764</v>
+      </c>
+      <c r="C180" t="s">
+        <v>783</v>
+      </c>
+      <c r="D180" t="s">
+        <v>810</v>
+      </c>
+      <c r="E180" t="s">
+        <v>844</v>
+      </c>
+      <c r="F180" t="s">
+        <v>569</v>
+      </c>
+      <c r="G180" t="s">
+        <v>400</v>
+      </c>
+      <c r="H180" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>732</v>
+      </c>
+      <c r="B181" t="s">
+        <v>765</v>
+      </c>
+      <c r="C181" t="s">
+        <v>403</v>
+      </c>
+      <c r="D181" t="s">
+        <v>811</v>
+      </c>
+      <c r="E181" t="s">
+        <v>845</v>
+      </c>
+      <c r="F181" t="s">
+        <v>29</v>
+      </c>
+      <c r="G181" t="s">
+        <v>406</v>
+      </c>
+      <c r="H181" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>733</v>
+      </c>
+      <c r="B182" t="s">
+        <v>766</v>
+      </c>
+      <c r="C182" t="s">
+        <v>77</v>
+      </c>
+      <c r="D182" t="s">
+        <v>812</v>
+      </c>
+      <c r="E182" t="s">
+        <v>846</v>
+      </c>
+      <c r="F182" t="s">
+        <v>29</v>
+      </c>
+      <c r="G182" t="s">
+        <v>455</v>
+      </c>
+      <c r="H182" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>734</v>
+      </c>
+      <c r="B183" t="s">
+        <v>767</v>
+      </c>
+      <c r="C183" t="s">
+        <v>77</v>
+      </c>
+      <c r="D183" t="s">
+        <v>813</v>
+      </c>
+      <c r="E183" t="s">
+        <v>847</v>
+      </c>
+      <c r="F183" t="s">
+        <v>29</v>
+      </c>
+      <c r="G183" t="s">
+        <v>400</v>
+      </c>
+      <c r="H183" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>735</v>
+      </c>
+      <c r="B184" t="s">
+        <v>768</v>
+      </c>
+      <c r="C184" t="s">
+        <v>18</v>
+      </c>
+      <c r="D184" t="s">
+        <v>814</v>
+      </c>
+      <c r="E184" t="s">
+        <v>848</v>
+      </c>
+      <c r="F184" t="s">
+        <v>29</v>
+      </c>
+      <c r="G184" t="s">
+        <v>411</v>
+      </c>
+      <c r="H184" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>736</v>
+      </c>
+      <c r="B185" t="s">
+        <v>769</v>
+      </c>
+      <c r="C185" t="s">
+        <v>255</v>
+      </c>
+      <c r="D185" t="s">
+        <v>815</v>
+      </c>
+      <c r="E185" t="s">
+        <v>624</v>
+      </c>
+      <c r="F185" t="s">
+        <v>29</v>
+      </c>
+      <c r="H185" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>737</v>
+      </c>
+      <c r="B186" t="s">
+        <v>113</v>
+      </c>
+      <c r="C186" t="s">
+        <v>403</v>
+      </c>
+      <c r="D186" t="s">
+        <v>816</v>
+      </c>
+      <c r="E186" t="s">
+        <v>849</v>
+      </c>
+      <c r="F186" t="s">
+        <v>29</v>
+      </c>
+      <c r="H186" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>738</v>
+      </c>
+      <c r="B187" t="s">
+        <v>770</v>
+      </c>
+      <c r="C187" t="s">
+        <v>577</v>
+      </c>
+      <c r="D187" t="s">
+        <v>817</v>
+      </c>
+      <c r="E187" t="s">
+        <v>850</v>
+      </c>
+      <c r="F187" t="s">
+        <v>29</v>
+      </c>
+      <c r="H187" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>739</v>
+      </c>
+      <c r="B188" t="s">
+        <v>771</v>
+      </c>
+      <c r="C188" t="s">
+        <v>784</v>
+      </c>
+      <c r="D188" t="s">
+        <v>818</v>
+      </c>
+      <c r="E188" t="s">
+        <v>851</v>
+      </c>
+      <c r="F188" t="s">
+        <v>29</v>
+      </c>
+      <c r="H188" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I156" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I154 I156 I155" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>